--- a/Contenidos_Consultados/output/contenidos_consultados_detalle_febrero_2026.xlsx
+++ b/Contenidos_Consultados/output/contenidos_consultados_detalle_febrero_2026.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E924"/>
+  <dimension ref="A1:E940"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B1" s="2" t="n">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>9031</v>
+        <v>9382</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>0.004561509667258806</v>
+        <v>0.004738797884865698</v>
       </c>
     </row>
     <row r="41">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>7824</v>
+        <v>7899</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>0.003951860440331403</v>
+        <v>0.003989742538110653</v>
       </c>
     </row>
     <row r="49">
@@ -1224,27 +1224,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MO04CUX01 Hacer la VTV</t>
+          <t>AC04CUX01 Apertura 147</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>5355</v>
+        <v>5187</v>
       </c>
       <c r="C60" s="6" t="n">
-        <v>0.002704781781438479</v>
+        <v>0.002619925882412958</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AC04CUX01 Apertura 147</t>
+          <t>MO04CUX01 Hacer la VTV</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>5187</v>
+        <v>5169</v>
       </c>
       <c r="C61" s="6" t="n">
-        <v>0.002619925882412958</v>
+        <v>0.002610834178945938</v>
       </c>
     </row>
     <row r="62">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="B69" s="5" t="n">
-        <v>3959</v>
+        <v>3899</v>
       </c>
       <c r="C69" s="6" t="n">
-        <v>0.001999669668107365</v>
+        <v>0.001969363989883965</v>
       </c>
     </row>
     <row r="70">
@@ -1601,53 +1601,53 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MO04CUX02 Apertura</t>
+          <t>SUA01CUX00  Arreglos</t>
         </is>
       </c>
       <c r="B89" s="5" t="n">
-        <v>3066</v>
+        <v>3074</v>
       </c>
       <c r="C89" s="6" t="n">
-        <v>0.001548620157215757</v>
+        <v>0.00155266091431221</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EDU04CUX05 Apertura</t>
+          <t>MO04CUX02 Apertura</t>
         </is>
       </c>
       <c r="B90" s="5" t="n">
-        <v>3043</v>
+        <v>3066</v>
       </c>
       <c r="C90" s="6" t="n">
-        <v>0.001537002980563453</v>
+        <v>0.001548620157215757</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MO08CUX03  Más de TelePASE</t>
+          <t>EDU04CUX05 Apertura</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
-        <v>3038</v>
+        <v>3043</v>
       </c>
       <c r="C91" s="6" t="n">
-        <v>0.00153447750737817</v>
+        <v>0.001537002980563453</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SUA01CUX00  Arreglos</t>
+          <t>MO08CUX03  Más de TelePASE</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
-        <v>3003</v>
+        <v>3038</v>
       </c>
       <c r="C92" s="6" t="n">
-        <v>0.001516799195081186</v>
+        <v>0.00153447750737817</v>
       </c>
     </row>
     <row r="93">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="B96" s="5" t="n">
-        <v>2677</v>
+        <v>2654</v>
       </c>
       <c r="C96" s="6" t="n">
-        <v>0.001352138343400711</v>
+        <v>0.001340521166748408</v>
       </c>
     </row>
     <row r="97">
@@ -1978,7 +1978,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SE00CUX01 Apertura</t>
+          <t>SUA01CUX Pedido de dirección</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
@@ -1991,7 +1991,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SUA01CUX Pedido de dirección</t>
+          <t>SE00CUX01 Apertura</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
@@ -2043,72 +2043,72 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SIGEHOS &gt; ✅ Operador disponible</t>
+          <t>ED04CUX15 Apertura</t>
         </is>
       </c>
       <c r="B123" s="5" t="n">
-        <v>1761</v>
+        <v>1748</v>
       </c>
       <c r="C123" s="6" t="n">
-        <v>0.0008894716558567996</v>
+        <v>0.0008829054255750628</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ED04CUX15 Apertura</t>
+          <t>DH01CUX01 Subsidio Habitacional 690</t>
         </is>
       </c>
       <c r="B124" s="5" t="n">
-        <v>1748</v>
+        <v>1735</v>
       </c>
       <c r="C124" s="6" t="n">
-        <v>0.0008829054255750628</v>
+        <v>0.0008763391952933262</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DH01CUX01 Subsidio Habitacional 690</t>
+          <t>AG01CUX01 Reliquidación boletas patentes</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
-        <v>1735</v>
+        <v>1715</v>
       </c>
       <c r="C125" s="6" t="n">
-        <v>0.0008763391952933262</v>
+        <v>0.0008662373025521927</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AG01CUX01 Reliquidación boletas patentes</t>
+          <t>SIGEHOS &gt; ✅ Operador disponible</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
-        <v>1715</v>
+        <v>1690</v>
       </c>
       <c r="C126" s="6" t="n">
-        <v>0.0008662373025521927</v>
+        <v>0.0008536099366257759</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>INN10CUX06 Validación audios largos</t>
+          <t>MO04CUX01 Cómo sacar turno</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
-        <v>1669</v>
+        <v>1684</v>
       </c>
       <c r="C127" s="6" t="n">
-        <v>0.0008430029492475857</v>
+        <v>0.0008505793688034359</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MO04CUX05 Apertura</t>
+          <t>INN10CUX06 Validación audios largos</t>
         </is>
       </c>
       <c r="B128" s="5" t="n">
@@ -2121,66 +2121,66 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TR01CUX21 Apertura</t>
+          <t>MO04CUX05 Apertura</t>
         </is>
       </c>
       <c r="B129" s="5" t="n">
-        <v>1655</v>
+        <v>1669</v>
       </c>
       <c r="C129" s="6" t="n">
-        <v>0.0008359316243287924</v>
+        <v>0.0008430029492475857</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SUA01CUX21 Apertura</t>
+          <t>TR01CUX21 Apertura</t>
         </is>
       </c>
       <c r="B130" s="5" t="n">
-        <v>1645</v>
+        <v>1655</v>
       </c>
       <c r="C130" s="6" t="n">
-        <v>0.0008308806779582257</v>
+        <v>0.0008359316243287924</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Fuera de horario de atención AGIP</t>
+          <t>SUA01CUX21 Apertura</t>
         </is>
       </c>
       <c r="B131" s="5" t="n">
-        <v>1601</v>
+        <v>1645</v>
       </c>
       <c r="C131" s="6" t="n">
-        <v>0.0008086565139277321</v>
+        <v>0.0008308806779582257</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>TR04CUX23 Apertura</t>
+          <t>Fuera de horario de atención AGIP</t>
         </is>
       </c>
       <c r="B132" s="5" t="n">
-        <v>1525</v>
+        <v>1601</v>
       </c>
       <c r="C132" s="6" t="n">
-        <v>0.000770269321511425</v>
+        <v>0.0008086565139277321</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>DH03CUX01 Apertura</t>
+          <t>TR04CUX23 Apertura</t>
         </is>
       </c>
       <c r="B133" s="5" t="n">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="C133" s="6" t="n">
-        <v>0.0007697642268743683</v>
+        <v>0.000770269321511425</v>
       </c>
     </row>
     <row r="134">
@@ -2199,14 +2199,14 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MO04CUX01 Cómo sacar turno</t>
+          <t>DH03CUX01 Apertura</t>
         </is>
       </c>
       <c r="B135" s="5" t="n">
-        <v>1498</v>
+        <v>1524</v>
       </c>
       <c r="C135" s="6" t="n">
-        <v>0.0007566317663108949</v>
+        <v>0.0007697642268743683</v>
       </c>
     </row>
     <row r="136">
@@ -2472,7 +2472,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>INN08CUX01 Apertura por webchat DEMO</t>
+          <t>SA05CUX01 Apertura</t>
         </is>
       </c>
       <c r="B156" s="5" t="n">
@@ -2485,7 +2485,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SA05CUX01 Apertura</t>
+          <t>INN08CUX01 Apertura por webchat DEMO</t>
         </is>
       </c>
       <c r="B157" s="5" t="n">
@@ -2537,7 +2537,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SUA01CUX08 Apertura</t>
+          <t>MO04CUX03 Apertura</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
@@ -2550,7 +2550,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MO04CUX03 Apertura</t>
+          <t>SUA01CUX08 Apertura</t>
         </is>
       </c>
       <c r="B162" s="5" t="n">
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="B174" s="5" t="n">
-        <v>856</v>
+        <v>870</v>
       </c>
       <c r="C174" s="6" t="n">
-        <v>0.0004323610093205114</v>
+        <v>0.0004394323342393048</v>
       </c>
     </row>
     <row r="175">
@@ -2732,40 +2732,40 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SE02CUX04 Apertura</t>
+          <t>CIU05CUX03 Retiro</t>
         </is>
       </c>
       <c r="B176" s="5" t="n">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="C176" s="6" t="n">
-        <v>0.0004288253468611146</v>
+        <v>0.0004318559146834547</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Error general acciones de código</t>
+          <t>SE02CUX04 Apertura</t>
         </is>
       </c>
       <c r="B177" s="5" t="n">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C177" s="6" t="n">
-        <v>0.0004273100629499446</v>
+        <v>0.0004288253468611146</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>DH03CUX02 Apertura</t>
+          <t>Error general acciones de código</t>
         </is>
       </c>
       <c r="B178" s="5" t="n">
-        <v>834</v>
+        <v>846</v>
       </c>
       <c r="C178" s="6" t="n">
-        <v>0.0004212489273052646</v>
+        <v>0.0004273100629499446</v>
       </c>
     </row>
     <row r="179">
@@ -2784,53 +2784,53 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MO05CUX13 Chequeo turno</t>
+          <t>DH03CUX02 Apertura</t>
         </is>
       </c>
       <c r="B180" s="5" t="n">
-        <v>811</v>
+        <v>834</v>
       </c>
       <c r="C180" s="6" t="n">
-        <v>0.0004096317506529611</v>
+        <v>0.0004212489273052646</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>DDHH03CUX07 Apertura</t>
+          <t>MO05CUX13 Chequeo turno</t>
         </is>
       </c>
       <c r="B181" s="5" t="n">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C181" s="6" t="n">
-        <v>0.0004081164667417911</v>
+        <v>0.0004096317506529611</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SA08CUX01 Campañas de donación</t>
+          <t>DDHH03CUX07 Apertura</t>
         </is>
       </c>
       <c r="B182" s="5" t="n">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C182" s="6" t="n">
-        <v>0.0004071062774676778</v>
+        <v>0.0004081164667417911</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CIU05CUX03 Retiro</t>
+          <t>SA08CUX01 Campañas de donación</t>
         </is>
       </c>
       <c r="B183" s="5" t="n">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="C183" s="6" t="n">
-        <v>0.0004045808042823944</v>
+        <v>0.0004066011828306211</v>
       </c>
     </row>
     <row r="184">
@@ -2940,7 +2940,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>DH09CUX01 Apertura</t>
+          <t>SUA01CUX34 Vaciado de contenedor</t>
         </is>
       </c>
       <c r="B192" s="5" t="n">
@@ -2953,7 +2953,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SUA01CUX34 Vaciado de contenedor</t>
+          <t>DH09CUX01 Apertura</t>
         </is>
       </c>
       <c r="B193" s="5" t="n">
@@ -3122,40 +3122,40 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>EDU05CUX06 Apertura</t>
+          <t>Permitido estacionar por ubicación actual</t>
         </is>
       </c>
       <c r="B206" s="5" t="n">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="C206" s="6" t="n">
-        <v>0.0003338675550944603</v>
+        <v>0.0003323522711832902</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Permitido estacionar por ubicación actual</t>
+          <t>AGC02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B207" s="5" t="n">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="C207" s="6" t="n">
-        <v>0.0003323522711832902</v>
+        <v>0.0003293217033609502</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>AGC02CUX01 Apertura</t>
+          <t>EDU05CUX06 Apertura</t>
         </is>
       </c>
       <c r="B208" s="5" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C208" s="6" t="n">
-        <v>0.0003293217033609502</v>
+        <v>0.0003278064194497802</v>
       </c>
     </row>
     <row r="209">
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="B211" s="5" t="n">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="C211" s="6" t="n">
-        <v>0.0003156841481604201</v>
+        <v>0.0003197249052568734</v>
       </c>
     </row>
     <row r="212">
@@ -3252,53 +3252,53 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>CU08CUX07 Agenda carnaval</t>
+          <t>IN01CUX01 Apertura de contingencia</t>
         </is>
       </c>
       <c r="B216" s="5" t="n">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C216" s="6" t="n">
-        <v>0.0002904294163075865</v>
+        <v>0.0002894192270334731</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>SA07CUX01 Hepatitis B</t>
+          <t>CU01CUX06 Apertura</t>
         </is>
       </c>
       <c r="B217" s="5" t="n">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C217" s="6" t="n">
-        <v>0.0002899243216705298</v>
+        <v>0.0002889141323964165</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>IN01CUX01 Apertura de contingencia</t>
+          <t>CU08CUX07 Agenda carnaval</t>
         </is>
       </c>
       <c r="B218" s="5" t="n">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="C218" s="6" t="n">
-        <v>0.0002894192270334731</v>
+        <v>0.0002863886592111331</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>CU01CUX06 Apertura</t>
+          <t>EM01CUX02 Apertura</t>
         </is>
       </c>
       <c r="B219" s="5" t="n">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="C219" s="6" t="n">
-        <v>0.0002889141323964165</v>
+        <v>0.0002833580913887931</v>
       </c>
     </row>
     <row r="220">
@@ -3317,20 +3317,20 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>EM01CUX02 Apertura</t>
+          <t>RC01CUX06 Apertura</t>
         </is>
       </c>
       <c r="B221" s="5" t="n">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C221" s="6" t="n">
-        <v>0.0002833580913887931</v>
+        <v>0.0002813377128405664</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>RC01CUX06 Apertura</t>
+          <t>EDU02CUX09 Apertura</t>
         </is>
       </c>
       <c r="B222" s="5" t="n">
@@ -3343,14 +3343,14 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>EDU02CUX09 Apertura</t>
+          <t>SA07CUX01 Hepatitis B</t>
         </is>
       </c>
       <c r="B223" s="5" t="n">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C223" s="6" t="n">
-        <v>0.0002813377128405664</v>
+        <v>0.0002808326182035097</v>
       </c>
     </row>
     <row r="224">
@@ -3564,7 +3564,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>IN02CUX02 Apertura</t>
+          <t>CIU05CUX09 Apertura</t>
         </is>
       </c>
       <c r="B240" s="5" t="n">
@@ -3577,7 +3577,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>CU09CUX01 CCK</t>
+          <t>IN02CUX02 Apertura</t>
         </is>
       </c>
       <c r="B241" s="5" t="n">
@@ -3590,85 +3590,85 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>CIU05CUX09 Apertura</t>
+          <t>MO01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B242" s="5" t="n">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C242" s="6" t="n">
-        <v>0.0002474963721577693</v>
+        <v>0.0002459810882465993</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>MO01CUX01 Apertura</t>
+          <t>MO05CUX12 Apertura</t>
         </is>
       </c>
       <c r="B243" s="5" t="n">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C243" s="6" t="n">
-        <v>0.0002459810882465993</v>
+        <v>0.0002439607096983726</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>MO05CUX12 Apertura</t>
+          <t>CU08CUX06 Verano Joven BA</t>
         </is>
       </c>
       <c r="B244" s="5" t="n">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C244" s="6" t="n">
-        <v>0.0002439607096983726</v>
+        <v>0.000243455615061316</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>CU08CUX06 Verano Joven BA</t>
+          <t>EP05CUX02 Apertura</t>
         </is>
       </c>
       <c r="B245" s="5" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C245" s="6" t="n">
-        <v>0.000243455615061316</v>
+        <v>0.0002429505204242593</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>EP05CUX02 Apertura</t>
+          <t>Error Permitido Estacionar</t>
         </is>
       </c>
       <c r="B246" s="5" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C246" s="6" t="n">
-        <v>0.0002429505204242593</v>
+        <v>0.0002414352365130893</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Error Permitido Estacionar</t>
+          <t>TR01CUX14 Apertura</t>
         </is>
       </c>
       <c r="B247" s="5" t="n">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C247" s="6" t="n">
-        <v>0.0002414352365130893</v>
+        <v>0.0002404250472389759</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>TR01CUX14 Apertura</t>
+          <t>SE07CUX01 Policía</t>
         </is>
       </c>
       <c r="B248" s="5" t="n">
@@ -3681,105 +3681,105 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>SE07CUX01 Policía</t>
+          <t>CU09CUX01 CCK</t>
         </is>
       </c>
       <c r="B249" s="5" t="n">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C249" s="6" t="n">
-        <v>0.0002404250472389759</v>
+        <v>0.0002378995740536926</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>SUA01CUX25 Apertura</t>
+          <t>TR02CUX12 Cómo es el trámite</t>
         </is>
       </c>
       <c r="B250" s="5" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C250" s="6" t="n">
-        <v>0.0002373944794166359</v>
+        <v>0.0002378995740536926</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>EDU03CUX08 Necesito ayuda</t>
+          <t>SUA01CUX25 Apertura</t>
         </is>
       </c>
       <c r="B251" s="5" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C251" s="6" t="n">
-        <v>0.0002368893847795792</v>
+        <v>0.0002373944794166359</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>TR02CUX12 Cómo es el trámite</t>
+          <t>EDU03CUX08 Necesito ayuda</t>
         </is>
       </c>
       <c r="B252" s="5" t="n">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C252" s="6" t="n">
-        <v>0.0002348690062313525</v>
+        <v>0.0002368893847795792</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>CU13CUX01 Apertura</t>
+          <t>EDU03CUX09 Apertura</t>
         </is>
       </c>
       <c r="B253" s="5" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C253" s="6" t="n">
-        <v>0.0002328486276831258</v>
+        <v>0.0002338588169572392</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Notificación digital</t>
+          <t>CU13CUX01 Apertura</t>
         </is>
       </c>
       <c r="B254" s="5" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C254" s="6" t="n">
-        <v>0.0002318384384090125</v>
+        <v>0.0002328486276831258</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>EDU04CUX06 Apertura</t>
+          <t>Notificación digital</t>
         </is>
       </c>
       <c r="B255" s="5" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C255" s="6" t="n">
-        <v>0.0002313333437719558</v>
+        <v>0.0002318384384090125</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>EDU03CUX09 Apertura</t>
+          <t>EDU04CUX06 Apertura</t>
         </is>
       </c>
       <c r="B256" s="5" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C256" s="6" t="n">
-        <v>0.0002308282491348992</v>
+        <v>0.0002313333437719558</v>
       </c>
     </row>
     <row r="257">
@@ -3811,27 +3811,27 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>TR04CUX32  Primer pasaporte</t>
+          <t>MO01CUX02 Apertura</t>
         </is>
       </c>
       <c r="B259" s="5" t="n">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C259" s="6" t="n">
-        <v>0.0002252722081272758</v>
+        <v>0.0002232518295790491</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>MO01CUX02 Apertura</t>
+          <t>TUR01CUX05 Pago de BUI</t>
         </is>
       </c>
       <c r="B260" s="5" t="n">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C260" s="6" t="n">
-        <v>0.0002232518295790491</v>
+        <v>0.0002227467349419924</v>
       </c>
     </row>
     <row r="261">
@@ -3876,7 +3876,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>EDU03CUX05  Apertura</t>
+          <t>MO08CUX01 Apertura</t>
         </is>
       </c>
       <c r="B264" s="5" t="n">
@@ -3889,7 +3889,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>MO08CUX01 Apertura</t>
+          <t>SUA01CUX14 Apertura</t>
         </is>
       </c>
       <c r="B265" s="5" t="n">
@@ -3902,7 +3902,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>SUA01CUX14 Apertura</t>
+          <t>EDU03CUX05  Apertura</t>
         </is>
       </c>
       <c r="B266" s="5" t="n">
@@ -3915,53 +3915,53 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>TR04CUX41 Antecedentes penales</t>
+          <t>MO06CUX02 Apertura</t>
         </is>
       </c>
       <c r="B267" s="5" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C267" s="6" t="n">
-        <v>0.000214160126112029</v>
+        <v>0.0002146652207490857</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>DEC05CUX01 Apertura</t>
+          <t>TR04CUX41 Antecedentes penales</t>
         </is>
       </c>
       <c r="B268" s="5" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C268" s="6" t="n">
-        <v>0.0002136550314749723</v>
+        <v>0.000214160126112029</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>EDU04CUX24 Apertura</t>
+          <t>DEC05CUX01 Apertura</t>
         </is>
       </c>
       <c r="B269" s="5" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C269" s="6" t="n">
-        <v>0.0002131499368379156</v>
+        <v>0.0002136550314749723</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>TUR01CUX05 Pago de BUI</t>
+          <t>EDU04CUX24 Apertura</t>
         </is>
       </c>
       <c r="B270" s="5" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C270" s="6" t="n">
-        <v>0.000211129558289689</v>
+        <v>0.0002131499368379156</v>
       </c>
     </row>
     <row r="271">
@@ -3980,14 +3980,14 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>MO06CUX02 Apertura</t>
+          <t>TR04CUX32  Primer pasaporte</t>
         </is>
       </c>
       <c r="B272" s="5" t="n">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="C272" s="6" t="n">
-        <v>0.0002096142743785189</v>
+        <v>0.0002050684226450089</v>
       </c>
     </row>
     <row r="273">
@@ -4071,27 +4071,27 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>SUA01CUX00 Apertura corta</t>
+          <t>EDU03CUX06 Apertura</t>
         </is>
       </c>
       <c r="B279" s="5" t="n">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C279" s="6" t="n">
-        <v>0.0001949665299038754</v>
+        <v>0.0001944614352668188</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>EDU03CUX06 Apertura</t>
+          <t xml:space="preserve">CU08CUX07 Apertura </t>
         </is>
       </c>
       <c r="B280" s="5" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C280" s="6" t="n">
-        <v>0.0001944614352668188</v>
+        <v>0.0001929461513556488</v>
       </c>
     </row>
     <row r="281">
@@ -4123,7 +4123,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t xml:space="preserve">CU08CUX07 Apertura </t>
+          <t>DH11CUX01 Más cursos</t>
         </is>
       </c>
       <c r="B283" s="5" t="n">
@@ -4136,14 +4136,14 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>DH11CUX01 Más cursos</t>
+          <t>Tagear UsuarioPrueba</t>
         </is>
       </c>
       <c r="B284" s="5" t="n">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C284" s="6" t="n">
-        <v>0.0001889053942591954</v>
+        <v>0.0001868850157109687</v>
       </c>
     </row>
     <row r="285">
@@ -4162,66 +4162,66 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Tagear UsuarioPrueba</t>
+          <t>CU05CUX01 Apertura</t>
         </is>
       </c>
       <c r="B286" s="5" t="n">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C286" s="6" t="n">
-        <v>0.000186379921073912</v>
+        <v>0.0001853697317997987</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>CU05CUX01 Apertura</t>
+          <t>EP03CUX01  Apertura</t>
         </is>
       </c>
       <c r="B287" s="5" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C287" s="6" t="n">
-        <v>0.0001853697317997987</v>
+        <v>0.000184864637162742</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>EP03CUX01  Apertura</t>
+          <t>CIU02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B288" s="5" t="n">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C288" s="6" t="n">
-        <v>0.000184864637162742</v>
+        <v>0.0001843595425256853</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>CIU02CUX01 Apertura</t>
+          <t>EDU03CUX07 Apto psicofísico</t>
         </is>
       </c>
       <c r="B289" s="5" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C289" s="6" t="n">
-        <v>0.0001843595425256853</v>
+        <v>0.0001838544478886286</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>EDU03CUX07 Apto psicofísico</t>
+          <t>SUA01CUX19 Apertura</t>
         </is>
       </c>
       <c r="B290" s="5" t="n">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C290" s="6" t="n">
-        <v>0.0001838544478886286</v>
+        <v>0.0001828442586145153</v>
       </c>
     </row>
     <row r="291">
@@ -4240,40 +4240,40 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>SUA01CUX19 Apertura</t>
+          <t>TR03CUX16 Consorcios</t>
         </is>
       </c>
       <c r="B292" s="5" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C292" s="6" t="n">
-        <v>0.0001828442586145153</v>
+        <v>0.0001823391639774586</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>TR03CUX16 Consorcios</t>
+          <t>TR03CUX28 CUIL</t>
         </is>
       </c>
       <c r="B293" s="5" t="n">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C293" s="6" t="n">
-        <v>0.0001823391639774586</v>
+        <v>0.0001813289747033453</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>TR03CUX28 CUIL</t>
+          <t>CO10CUX02 Apertura post evento</t>
         </is>
       </c>
       <c r="B294" s="5" t="n">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C294" s="6" t="n">
-        <v>0.0001813289747033453</v>
+        <v>0.0001803187854292319</v>
       </c>
     </row>
     <row r="295">
@@ -4292,20 +4292,20 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>CO10CUX02 Apertura post evento</t>
+          <t>VI01CUX03 Apertura</t>
         </is>
       </c>
       <c r="B296" s="5" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C296" s="6" t="n">
-        <v>0.0001803187854292319</v>
+        <v>0.0001788035015180619</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>VI01CUX03 Apertura</t>
+          <t>TR03CUX12 Apertura</t>
         </is>
       </c>
       <c r="B297" s="5" t="n">
@@ -4318,235 +4318,235 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>TR03CUX12 Apertura</t>
+          <t>CU04CUX40 Apertura post evento</t>
         </is>
       </c>
       <c r="B298" s="5" t="n">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C298" s="6" t="n">
-        <v>0.0001788035015180619</v>
+        <v>0.0001742576497845519</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>TU04CUX01 Preapertura</t>
+          <t>EDU04CUX04 Apertura</t>
         </is>
       </c>
       <c r="B299" s="5" t="n">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C299" s="6" t="n">
-        <v>0.0001772882176068919</v>
+        <v>0.0001737525551474952</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>CU04CUX40 Apertura post evento</t>
+          <t xml:space="preserve"> SA17CUX01 Por ahora no</t>
         </is>
       </c>
       <c r="B300" s="5" t="n">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C300" s="6" t="n">
-        <v>0.0001742576497845519</v>
+        <v>0.0001722372712363252</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>EDU04CUX04 Apertura</t>
+          <t>Copia Digital de Expediente o Documento *Apertura</t>
         </is>
       </c>
       <c r="B301" s="5" t="n">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C301" s="6" t="n">
-        <v>0.0001737525551474952</v>
+        <v>0.0001707219873251552</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SA17CUX01 Por ahora no</t>
+          <t>SA02CUX01 Evaluación COVID-19</t>
         </is>
       </c>
       <c r="B302" s="5" t="n">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C302" s="6" t="n">
-        <v>0.0001722372712363252</v>
+        <v>0.0001687016087769285</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Copia Digital de Expediente o Documento *Apertura</t>
+          <t>Test IABA</t>
         </is>
       </c>
       <c r="B303" s="5" t="n">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="C303" s="6" t="n">
-        <v>0.0001722372712363252</v>
+        <v>0.0001666812302287018</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Test IABA</t>
+          <t>SA14CUX01 Apertura</t>
         </is>
       </c>
       <c r="B304" s="5" t="n">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C304" s="6" t="n">
-        <v>0.0001707219873251552</v>
+        <v>0.0001656710409545885</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>SA02CUX01 Evaluación COVID-19</t>
+          <t>MO03CUX01 Otros abonos y pases</t>
         </is>
       </c>
       <c r="B305" s="5" t="n">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C305" s="6" t="n">
-        <v>0.0001687016087769285</v>
+        <v>0.0001651659463175318</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>SA14CUX01 Apertura</t>
+          <t>SUA01CUX29 Apertura columnas en mal estado</t>
         </is>
       </c>
       <c r="B306" s="5" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C306" s="6" t="n">
-        <v>0.0001656710409545885</v>
+        <v>0.0001651659463175318</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>MO03CUX01 Otros abonos y pases</t>
+          <t>SUA01CUX17 Apertura</t>
         </is>
       </c>
       <c r="B307" s="5" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C307" s="6" t="n">
-        <v>0.0001651659463175318</v>
+        <v>0.0001646608516804751</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>SUA01CUX29 Apertura columnas en mal estado</t>
+          <t>SA10CUX03 Mapa de Salud</t>
         </is>
       </c>
       <c r="B308" s="5" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C308" s="6" t="n">
-        <v>0.0001651659463175318</v>
+        <v>0.0001646608516804751</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>SA10CUX03 Mapa de Salud</t>
+          <t>TR04CUX07 Apertura</t>
         </is>
       </c>
       <c r="B309" s="5" t="n">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C309" s="6" t="n">
-        <v>0.0001646608516804751</v>
+        <v>0.0001616302838581351</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>SUA01CUX17 Apertura</t>
+          <t>TR03CUX03 Proescritores</t>
         </is>
       </c>
       <c r="B310" s="5" t="n">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="C310" s="6" t="n">
-        <v>0.0001646608516804751</v>
+        <v>0.0001606200945840217</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>TR04CUX07 Apertura</t>
+          <t>SE06CUX01 Apertura</t>
         </is>
       </c>
       <c r="B311" s="5" t="n">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C311" s="6" t="n">
-        <v>0.0001616302838581351</v>
+        <v>0.0001606200945840217</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>SE06CUX01 Apertura</t>
+          <t>SUA01CUX00 Apertura corta</t>
         </is>
       </c>
       <c r="B312" s="5" t="n">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C312" s="6" t="n">
-        <v>0.0001606200945840217</v>
+        <v>0.0001591048106728517</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>TR03CUX03 Proescritores</t>
+          <t>Flow fulfilled of "Primera vez"</t>
         </is>
       </c>
       <c r="B313" s="5" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C313" s="6" t="n">
-        <v>0.0001596099053099084</v>
+        <v>0.0001591048106728517</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Flow fulfilled of "Primera vez"</t>
+          <t>INN01CUX02 Apertura</t>
         </is>
       </c>
       <c r="B314" s="5" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C314" s="6" t="n">
-        <v>0.0001591048106728517</v>
+        <v>0.000158599716035795</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>INN01CUX02 Apertura</t>
+          <t>CU06CUX03 Apertura</t>
         </is>
       </c>
       <c r="B315" s="5" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C315" s="6" t="n">
-        <v>0.000158599716035795</v>
+        <v>0.0001580946213987384</v>
       </c>
     </row>
     <row r="316">
@@ -4565,72 +4565,72 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>CU06CUX03 Apertura</t>
+          <t>CIU04CUX01 Apertura</t>
         </is>
       </c>
       <c r="B317" s="5" t="n">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C317" s="6" t="n">
-        <v>0.0001580946213987384</v>
+        <v>0.0001565793374875684</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>CIU04CUX01 Apertura</t>
+          <t>TR02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B318" s="5" t="n">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C318" s="6" t="n">
-        <v>0.0001565793374875684</v>
+        <v>0.000152538580391115</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>TR02CUX01 Apertura</t>
+          <t>EDU01CUX03 Apertura</t>
         </is>
       </c>
       <c r="B319" s="5" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C319" s="6" t="n">
-        <v>0.000152538580391115</v>
+        <v>0.0001515283911170016</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>EDU01CUX03 Apertura</t>
+          <t>DH03CUX02 Qué necesito</t>
         </is>
       </c>
       <c r="B320" s="5" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C320" s="6" t="n">
-        <v>0.0001515283911170016</v>
+        <v>0.0001505182018428883</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>DH03CUX02 Qué necesito</t>
+          <t>AGC02CUX02 Director de Obra</t>
         </is>
       </c>
       <c r="B321" s="5" t="n">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C321" s="6" t="n">
-        <v>0.0001505182018428883</v>
+        <v>0.0001490029179317183</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>AGC02CUX02 Director de Obra</t>
+          <t>AGC01CUX02  Apertura</t>
         </is>
       </c>
       <c r="B322" s="5" t="n">
@@ -4643,40 +4643,40 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>AGC01CUX02  Apertura</t>
+          <t>JU01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B323" s="5" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C323" s="6" t="n">
-        <v>0.0001490029179317183</v>
+        <v>0.0001479927286576049</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>JU01CUX01 Apertura</t>
+          <t>CU09CUX04 Apertura</t>
         </is>
       </c>
       <c r="B324" s="5" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C324" s="6" t="n">
-        <v>0.0001479927286576049</v>
+        <v>0.0001474876340205483</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>CU09CUX04 Apertura</t>
+          <t>Flow fulfilled of "Happy Path"</t>
         </is>
       </c>
       <c r="B325" s="5" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C325" s="6" t="n">
-        <v>0.0001474876340205483</v>
+        <v>0.0001464774447464349</v>
       </c>
     </row>
     <row r="326">
@@ -4708,14 +4708,14 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Flow fulfilled of "Happy Path"</t>
+          <t>SIGEHOS &gt; ⏳ Espero</t>
         </is>
       </c>
       <c r="B328" s="5" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C328" s="6" t="n">
-        <v>0.0001454672554723216</v>
+        <v>0.0001439519715611516</v>
       </c>
     </row>
     <row r="329">
@@ -4747,150 +4747,150 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>AM04CUX05  Apertura</t>
+          <t>DH01CUX04 Pregunta 1</t>
         </is>
       </c>
       <c r="B331" s="5" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C331" s="6" t="n">
-        <v>0.0001373857412794148</v>
+        <v>0.0001389010251905848</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>SUA01CUX34 Lavado de contenedor</t>
+          <t>AM04CUX05  Apertura</t>
         </is>
       </c>
       <c r="B332" s="5" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C332" s="6" t="n">
-        <v>0.0001363755520053015</v>
+        <v>0.0001373857412794148</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>VI03CUX01 Apertura</t>
+          <t>SA07CUX01 Anticonceptivos</t>
         </is>
       </c>
       <c r="B333" s="5" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C333" s="6" t="n">
-        <v>0.0001363755520053015</v>
+        <v>0.0001373857412794148</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>DH01CUX04 Pregunta 1</t>
+          <t>SUA01CUX34 Lavado de contenedor</t>
         </is>
       </c>
       <c r="B334" s="5" t="n">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C334" s="6" t="n">
-        <v>0.0001328398895459048</v>
+        <v>0.0001363755520053015</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>VI01CUX01 Apertura</t>
+          <t>VI03CUX01 Apertura</t>
         </is>
       </c>
       <c r="B335" s="5" t="n">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C335" s="6" t="n">
-        <v>0.0001328398895459048</v>
+        <v>0.0001358704573682448</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Número de Documento Inválido | Estado de Trámites</t>
+          <t>VI01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B336" s="5" t="n">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C336" s="6" t="n">
-        <v>0.0001323347949088481</v>
+        <v>0.0001353653627311881</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>SUA01CUX12 Apertura</t>
+          <t>Número de Documento Inválido | Estado de Trámites</t>
         </is>
       </c>
       <c r="B337" s="5" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C337" s="6" t="n">
-        <v>0.0001308195109976781</v>
+        <v>0.0001323347949088481</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>SA07CUX01 Anticonceptivos</t>
+          <t>SUA01CUX12 Apertura</t>
         </is>
       </c>
       <c r="B338" s="5" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C338" s="6" t="n">
-        <v>0.0001282940378123947</v>
+        <v>0.0001308195109976781</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>CU11CUX03 Apertura</t>
+          <t>DE05CUX02 Qué actividades hay</t>
         </is>
       </c>
       <c r="B339" s="5" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C339" s="6" t="n">
-        <v>0.0001282940378123947</v>
+        <v>0.0001293042270865081</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>DH03CUX03 Apertura</t>
+          <t>CU11CUX03 Apertura</t>
         </is>
       </c>
       <c r="B340" s="5" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C340" s="6" t="n">
-        <v>0.0001272838485382814</v>
+        <v>0.0001277889431753381</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>SIGEHOS &gt;❌ Fuera de Horario</t>
+          <t>DH03CUX03 Apertura</t>
         </is>
       </c>
       <c r="B341" s="5" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C341" s="6" t="n">
-        <v>0.0001267787539012247</v>
+        <v>0.0001272838485382814</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>TR04CUX31 Qué necesito</t>
+          <t>SIGEHOS &gt;❌ Fuera de Horario</t>
         </is>
       </c>
       <c r="B342" s="5" t="n">
@@ -4916,105 +4916,105 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>GA04CUX17 Apertura</t>
+          <t>TR04CUX31 Qué necesito</t>
         </is>
       </c>
       <c r="B344" s="5" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C344" s="6" t="n">
-        <v>0.000123243091441828</v>
+        <v>0.0001257685646271113</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>TR03CUX22 Apertura</t>
+          <t>GA04CUX17 Apertura</t>
         </is>
       </c>
       <c r="B345" s="5" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C345" s="6" t="n">
-        <v>0.0001227379968047713</v>
+        <v>0.000123243091441828</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>CU08CUX06 Apertura</t>
+          <t>TR03CUX22 Apertura</t>
         </is>
       </c>
       <c r="B346" s="5" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C346" s="6" t="n">
-        <v>0.000120212523619488</v>
+        <v>0.000121727807530658</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>DE00CUX03 Apertura</t>
+          <t>CU08CUX06 Apertura</t>
         </is>
       </c>
       <c r="B347" s="5" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C347" s="6" t="n">
-        <v>0.0001197074289824313</v>
+        <v>0.000120212523619488</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>DE05CUX02 Qué actividades hay</t>
+          <t>SUA01CUX36 Reparación de semaforo</t>
         </is>
       </c>
       <c r="B348" s="5" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C348" s="6" t="n">
-        <v>0.000118697239708318</v>
+        <v>0.0001181921450712613</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>SUA01CUX36 Reparación de semaforo</t>
+          <t>DE00CUX03 Apertura</t>
         </is>
       </c>
       <c r="B349" s="5" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C349" s="6" t="n">
-        <v>0.0001181921450712613</v>
+        <v>0.0001176870504342046</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>limpiar variables</t>
+          <t>CU01CUX14 Apertura Estático</t>
         </is>
       </c>
       <c r="B350" s="5" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C350" s="6" t="n">
-        <v>0.0001146564826118646</v>
+        <v>0.0001166768611600913</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>CU01CUX14 Apertura Estático</t>
+          <t>limpiar variables</t>
         </is>
       </c>
       <c r="B351" s="5" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C351" s="6" t="n">
-        <v>0.0001141513879748079</v>
+        <v>0.0001146564826118646</v>
       </c>
     </row>
     <row r="352">
@@ -5050,10 +5050,10 @@
         </is>
       </c>
       <c r="B354" s="5" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C354" s="6" t="n">
-        <v>0.0001136462933377512</v>
+        <v>0.0001131411987006945</v>
       </c>
     </row>
     <row r="355">
@@ -5089,10 +5089,10 @@
         </is>
       </c>
       <c r="B357" s="5" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C357" s="6" t="n">
-        <v>0.0001106157255154112</v>
+        <v>0.0001121310094265812</v>
       </c>
     </row>
     <row r="358">
@@ -5128,36 +5128,36 @@
         </is>
       </c>
       <c r="B360" s="5" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C360" s="6" t="n">
-        <v>0.0001085953469671845</v>
+        <v>0.0001096055362412978</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>SIGEHOS &gt; ⏳ Espero</t>
+          <t>CU04CUX01 Apertura</t>
         </is>
       </c>
       <c r="B361" s="5" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C361" s="6" t="n">
-        <v>0.0001080902523301278</v>
+        <v>0.0001060698737819011</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>CU04CUX01 Apertura</t>
+          <t xml:space="preserve">EDU04CUX30 Niñez </t>
         </is>
       </c>
       <c r="B362" s="5" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C362" s="6" t="n">
-        <v>0.0001060698737819011</v>
+        <v>0.0001040494952336745</v>
       </c>
     </row>
     <row r="363">
@@ -5176,14 +5176,14 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>AGC01CUX00 Hacer una consulta</t>
+          <t>CU02CUX02 Apertura</t>
         </is>
       </c>
       <c r="B364" s="5" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C364" s="6" t="n">
-        <v>0.0001025342113225044</v>
+        <v>0.0001030393059595611</v>
       </c>
     </row>
     <row r="365">
@@ -5202,7 +5202,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>CU02CUX02 Apertura</t>
+          <t>TR01CUX10 Apertura</t>
         </is>
       </c>
       <c r="B366" s="5" t="n">
@@ -5215,14 +5215,14 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDU04CUX30 Niñez </t>
+          <t>CU01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B367" s="5" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C367" s="6" t="n">
-        <v>0.0001020291166854478</v>
+        <v>0.0001015240220483911</v>
       </c>
     </row>
     <row r="368">
@@ -5232,29 +5232,29 @@
         </is>
       </c>
       <c r="B368" s="5" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C368" s="6" t="n">
-        <v>0.0001020291166854478</v>
+        <v>0.0001015240220483911</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>CU01CUX01 Apertura</t>
+          <t>CIU02CUX01 Sedes comunales</t>
         </is>
       </c>
       <c r="B369" s="5" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C369" s="6" t="n">
-        <v>0.0001015240220483911</v>
+        <v>0.0001010189274113344</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>CIU02CUX01 Sedes comunales</t>
+          <t>AGC01CUX00 Hacer una consulta</t>
         </is>
       </c>
       <c r="B370" s="5" t="n">
@@ -5267,7 +5267,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>TR01CUX10 Apertura</t>
+          <t>TR03CUX30 Apertura</t>
         </is>
       </c>
       <c r="B371" s="5" t="n">
@@ -5280,7 +5280,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>TR03CUX30 Apertura</t>
+          <t>SUA01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B372" s="5" t="n">
@@ -5293,14 +5293,14 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>SUA01CUX01 Apertura</t>
+          <t xml:space="preserve">DH11CUX06 Apertura </t>
         </is>
       </c>
       <c r="B373" s="5" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C373" s="6" t="n">
-        <v>0.0001005138327742778</v>
+        <v>0.0001000087381372211</v>
       </c>
     </row>
     <row r="374">
@@ -5319,40 +5319,40 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t xml:space="preserve">DH11CUX06 Apertura </t>
+          <t>VI01CUX07 Apertura</t>
         </is>
       </c>
       <c r="B375" s="5" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C375" s="6" t="n">
-        <v>0.0001000087381372211</v>
+        <v>9.849345422605107e-05</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>VI01CUX07 Apertura</t>
+          <t>TR01CUX05 Apertura</t>
         </is>
       </c>
       <c r="B376" s="5" t="n">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C376" s="6" t="n">
-        <v>9.950364350016441e-05</v>
+        <v>9.59679810407677e-05</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>TR01CUX05 Apertura</t>
+          <t>DH06CUX01 Apertura</t>
         </is>
       </c>
       <c r="B377" s="5" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C377" s="6" t="n">
-        <v>9.59679810407677e-05</v>
+        <v>9.546288640371103e-05</v>
       </c>
     </row>
     <row r="378">
@@ -5371,131 +5371,131 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>DH06CUX01 Apertura</t>
+          <t>TR01CUX06 Apertura</t>
         </is>
       </c>
       <c r="B379" s="5" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C379" s="6" t="n">
-        <v>9.546288640371103e-05</v>
+        <v>9.445269712959768e-05</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>TR01CUX06 Apertura</t>
+          <t>TR01CUX08 Apertura</t>
         </is>
       </c>
       <c r="B380" s="5" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C380" s="6" t="n">
-        <v>9.445269712959768e-05</v>
+        <v>9.394760249254102e-05</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>TR01CUX08 Apertura</t>
+          <t>MO10CUX08 Apertura</t>
         </is>
       </c>
       <c r="B381" s="5" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C381" s="6" t="n">
-        <v>9.394760249254102e-05</v>
+        <v>9.344250785548434e-05</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>MO10CUX08 Apertura</t>
+          <t xml:space="preserve">SE01CUX05 Apertura </t>
         </is>
       </c>
       <c r="B382" s="5" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C382" s="6" t="n">
-        <v>9.344250785548434e-05</v>
+        <v>9.293741321842768e-05</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t xml:space="preserve">SE01CUX05 Apertura </t>
+          <t>Mensaje Otra Dirección | Permitido Estacionar</t>
         </is>
       </c>
       <c r="B383" s="5" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C383" s="6" t="n">
-        <v>9.293741321842768e-05</v>
+        <v>9.192722394431432e-05</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Mensaje Otra Dirección | Permitido Estacionar</t>
+          <t>Viaductos</t>
         </is>
       </c>
       <c r="B384" s="5" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C384" s="6" t="n">
-        <v>9.192722394431432e-05</v>
+        <v>9.091703467020098e-05</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Viaductos</t>
+          <t>TR03CUX26 Apertura</t>
         </is>
       </c>
       <c r="B385" s="5" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C385" s="6" t="n">
-        <v>9.091703467020098e-05</v>
+        <v>9.041194003314431e-05</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>DH11CUX03 Silencio user</t>
+          <t>Cariño</t>
         </is>
       </c>
       <c r="B386" s="5" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C386" s="6" t="n">
-        <v>9.041194003314431e-05</v>
+        <v>8.738137221080427e-05</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>TR03CUX26 Apertura</t>
+          <t>DH11CUX03 Silencio user</t>
         </is>
       </c>
       <c r="B387" s="5" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C387" s="6" t="n">
-        <v>8.990684539608764e-05</v>
+        <v>8.637118293669093e-05</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Cariño</t>
+          <t>AGC01CUX00  Apertura</t>
         </is>
       </c>
       <c r="B388" s="5" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C388" s="6" t="n">
-        <v>8.738137221080427e-05</v>
+        <v>8.586608829963425e-05</v>
       </c>
     </row>
     <row r="389">
@@ -5540,7 +5540,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>AGC01CUX00  Apertura</t>
+          <t>No esperar | AGIP</t>
         </is>
       </c>
       <c r="B392" s="5" t="n">
@@ -5553,40 +5553,40 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>No esperar | AGIP</t>
+          <t>CU09CUX01 Apertura</t>
         </is>
       </c>
       <c r="B393" s="5" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C393" s="6" t="n">
-        <v>8.435080438846425e-05</v>
+        <v>8.384570975140757e-05</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>GE01CUX03 Apertura</t>
+          <t>MO02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B394" s="5" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C394" s="6" t="n">
-        <v>8.384570975140757e-05</v>
+        <v>8.334061511435091e-05</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>CIU05CUX03 La Boca</t>
+          <t>GE01CUX03 Apertura</t>
         </is>
       </c>
       <c r="B395" s="5" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C395" s="6" t="n">
-        <v>8.283552047729423e-05</v>
+        <v>8.334061511435091e-05</v>
       </c>
     </row>
     <row r="396">
@@ -5618,20 +5618,20 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>GE03CUX02 Busco trabajo</t>
+          <t>MO10CUX02 Apertura</t>
         </is>
       </c>
       <c r="B398" s="5" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C398" s="6" t="n">
-        <v>8.283552047729423e-05</v>
+        <v>8.182533120318089e-05</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>MO10CUX02 Apertura</t>
+          <t>TU03CUX16  Apertura</t>
         </is>
       </c>
       <c r="B399" s="5" t="n">
@@ -5644,7 +5644,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>MO02CUX01 Apertura</t>
+          <t>EDU03CUX07 Declaración jurada</t>
         </is>
       </c>
       <c r="B400" s="5" t="n">
@@ -5657,150 +5657,150 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>TU03CUX16  Apertura</t>
+          <t>GE03CUX02 Busco trabajo</t>
         </is>
       </c>
       <c r="B401" s="5" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C401" s="6" t="n">
-        <v>8.182533120318089e-05</v>
+        <v>8.132023656612421e-05</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>EDU03CUX07 Declaración jurada</t>
+          <t>TU03CUX11 Apertura</t>
         </is>
       </c>
       <c r="B402" s="5" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C402" s="6" t="n">
-        <v>8.182533120318089e-05</v>
+        <v>8.132023656612421e-05</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>TU03CUX11 Apertura</t>
+          <t>DE01CUX02 Apertura post-evento</t>
         </is>
       </c>
       <c r="B403" s="5" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C403" s="6" t="n">
-        <v>8.132023656612421e-05</v>
+        <v>8.031004729201087e-05</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>DE01CUX02 Apertura post-evento</t>
+          <t>MO10CUX03 Apertura</t>
         </is>
       </c>
       <c r="B404" s="5" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C404" s="6" t="n">
-        <v>8.031004729201087e-05</v>
+        <v>7.879476338084084e-05</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>MO10CUX03 Apertura</t>
+          <t>CU03CUX04 Apertura</t>
         </is>
       </c>
       <c r="B405" s="5" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C405" s="6" t="n">
-        <v>7.879476338084084e-05</v>
+        <v>7.77845741067275e-05</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>CU03CUX04 Apertura</t>
+          <t>TUR01CUX06 Elegir tipo de turno</t>
         </is>
       </c>
       <c r="B406" s="5" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C406" s="6" t="n">
-        <v>7.77845741067275e-05</v>
+        <v>7.677438483261416e-05</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Suaci - Error de foto opcional</t>
+          <t>DH11CUX02 Apertura</t>
         </is>
       </c>
       <c r="B407" s="5" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C407" s="6" t="n">
-        <v>7.727947946967084e-05</v>
+        <v>7.62692901955575e-05</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>DH11CUX02 Apertura</t>
+          <t>TR03CUX07 Apertura Inscripción en el Registro Único de Instituciones Deportivas (RUID)</t>
         </is>
       </c>
       <c r="B408" s="5" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C408" s="6" t="n">
-        <v>7.727947946967084e-05</v>
+        <v>7.62692901955575e-05</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>TUR01CUX06 Elegir tipo de turno</t>
+          <t>DDHH02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B409" s="5" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C409" s="6" t="n">
-        <v>7.677438483261416e-05</v>
+        <v>7.62692901955575e-05</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>DDHH02CUX01 Apertura</t>
+          <t>DEC01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B410" s="5" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C410" s="6" t="n">
-        <v>7.62692901955575e-05</v>
+        <v>7.576419555850082e-05</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>DEC01CUX01 Apertura</t>
+          <t>Suaci - Error de foto opcional</t>
         </is>
       </c>
       <c r="B411" s="5" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C411" s="6" t="n">
-        <v>7.576419555850082e-05</v>
+        <v>7.525910092144414e-05</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>TR04CUX41 Mi argentina</t>
+          <t>DE02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B412" s="5" t="n">
@@ -5813,7 +5813,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>DDHH03CUX09 Apertura</t>
+          <t>TR04CUX41 Mi argentina</t>
         </is>
       </c>
       <c r="B413" s="5" t="n">
@@ -5826,248 +5826,248 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>DE02CUX01 Apertura</t>
+          <t>GA03CUX10 Apertura</t>
         </is>
       </c>
       <c r="B414" s="5" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C414" s="6" t="n">
-        <v>7.525910092144414e-05</v>
+        <v>7.475400628438748e-05</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>GA03CUX10 Apertura</t>
+          <t>CU04CUX32 Apertura post evento</t>
         </is>
       </c>
       <c r="B415" s="5" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C415" s="6" t="n">
-        <v>7.475400628438748e-05</v>
+        <v>7.42489116473308e-05</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>CU09CUX01 Apertura</t>
+          <t>DDHH03CUX09 Apertura</t>
         </is>
       </c>
       <c r="B416" s="5" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C416" s="6" t="n">
-        <v>7.42489116473308e-05</v>
+        <v>7.374381701027413e-05</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>CU04CUX32 Apertura post evento</t>
+          <t>AC02CUX02 Apertura</t>
         </is>
       </c>
       <c r="B417" s="5" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C417" s="6" t="n">
-        <v>7.42489116473308e-05</v>
+        <v>7.374381701027413e-05</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>AC02CUX02 Apertura</t>
+          <t>SE01CUX07 Apertura</t>
         </is>
       </c>
       <c r="B418" s="5" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C418" s="6" t="n">
-        <v>7.374381701027413e-05</v>
+        <v>7.323872237321746e-05</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>SE01CUX07 Apertura</t>
+          <t>Permiso de espectáculos musicales en vivo</t>
         </is>
       </c>
       <c r="B419" s="5" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C419" s="6" t="n">
-        <v>7.323872237321746e-05</v>
+        <v>7.273362773616079e-05</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>TR03CUX07 Apertura Inscripción en el Registro Único de Instituciones Deportivas (RUID)</t>
+          <t>CO02CUX02 Apertura</t>
         </is>
       </c>
       <c r="B420" s="5" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C420" s="6" t="n">
-        <v>7.323872237321746e-05</v>
+        <v>7.222853309910411e-05</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Permiso de espectáculos musicales en vivo</t>
+          <t>CU10CUX01 Apertura</t>
         </is>
       </c>
       <c r="B421" s="5" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C421" s="6" t="n">
-        <v>7.273362773616079e-05</v>
+        <v>7.121834382499077e-05</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>CO02CUX02 Apertura</t>
+          <t>EP05CUX01 Apertura</t>
         </is>
       </c>
       <c r="B422" s="5" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C422" s="6" t="n">
-        <v>7.222853309910411e-05</v>
+        <v>7.071324918793409e-05</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>CU10CUX01 Apertura</t>
+          <t>SE02CUX02 Apertura</t>
         </is>
       </c>
       <c r="B423" s="5" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C423" s="6" t="n">
-        <v>7.121834382499077e-05</v>
+        <v>7.071324918793409e-05</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>SE02CUX02 Apertura</t>
+          <t>SA11CUXO1 Plan de vacunación</t>
         </is>
       </c>
       <c r="B424" s="5" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C424" s="6" t="n">
-        <v>7.071324918793409e-05</v>
+        <v>6.970305991382075e-05</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>EP05CUX01 Apertura</t>
+          <t>AM02CUX03 Apertura</t>
         </is>
       </c>
       <c r="B425" s="5" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C425" s="6" t="n">
-        <v>7.071324918793409e-05</v>
+        <v>6.919796527676409e-05</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>AM02CUX03 Apertura</t>
+          <t>VI01CUX06 Apertura</t>
         </is>
       </c>
       <c r="B426" s="5" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C426" s="6" t="n">
-        <v>6.970305991382075e-05</v>
+        <v>6.818777600265073e-05</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>TR05CUX04 Apertura</t>
+          <t>DE03CUX02 Apertura</t>
         </is>
       </c>
       <c r="B427" s="5" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C427" s="6" t="n">
-        <v>6.970305991382075e-05</v>
+        <v>6.768268136559407e-05</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>VI01CUX06 Apertura</t>
+          <t>TR05CUX04 Apertura</t>
         </is>
       </c>
       <c r="B428" s="5" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C428" s="6" t="n">
-        <v>6.818777600265073e-05</v>
+        <v>6.768268136559407e-05</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>DE03CUX02 Apertura</t>
+          <t>TR03CUX06 Apertura</t>
         </is>
       </c>
       <c r="B429" s="5" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C429" s="6" t="n">
-        <v>6.768268136559407e-05</v>
+        <v>6.667249209148072e-05</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>TR03CUX06 Apertura</t>
+          <t>INN10CUX01 Apertura</t>
         </is>
       </c>
       <c r="B430" s="5" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C430" s="6" t="n">
-        <v>6.768268136559407e-05</v>
+        <v>6.616739745442405e-05</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>INN10CUX01 Apertura</t>
+          <t>SA16CUX02 Apertura</t>
         </is>
       </c>
       <c r="B431" s="5" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C431" s="6" t="n">
-        <v>6.616739745442405e-05</v>
+        <v>6.51572081803107e-05</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>SA16CUX02 Apertura</t>
+          <t>TR02CUX13 Qué necesito</t>
         </is>
       </c>
       <c r="B432" s="5" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C432" s="6" t="n">
-        <v>6.566230281736738e-05</v>
+        <v>6.51572081803107e-05</v>
       </c>
     </row>
     <row r="433">
@@ -6086,111 +6086,111 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>TR02CUX13 Qué necesito</t>
+          <t>TR04CUX32  Apertura</t>
         </is>
       </c>
       <c r="B434" s="5" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C434" s="6" t="n">
-        <v>6.212664035797068e-05</v>
+        <v>6.263173499502734e-05</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>TR02CUX13 Partida de defunción SD</t>
+          <t>TU03CUX01 Apertura fútbol</t>
         </is>
       </c>
       <c r="B435" s="5" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C435" s="6" t="n">
-        <v>6.212664035797068e-05</v>
+        <v>6.1621545720914e-05</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>TUR01CUX12 Preguntar género</t>
+          <t>CIU05CUX09 Parque Rivadavia</t>
         </is>
       </c>
       <c r="B436" s="5" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C436" s="6" t="n">
-        <v>6.1621545720914e-05</v>
+        <v>6.061135644680066e-05</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>TU03CUX01 Apertura fútbol</t>
+          <t>TR02CUX10 Confirmar trámite</t>
         </is>
       </c>
       <c r="B437" s="5" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C437" s="6" t="n">
-        <v>6.1621545720914e-05</v>
+        <v>5.960116717268731e-05</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>CIU05CUX09 Parque Rivadavia</t>
+          <t>MO06CUX03 Apertura</t>
         </is>
       </c>
       <c r="B438" s="5" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C438" s="6" t="n">
-        <v>6.061135644680066e-05</v>
+        <v>5.909607253563064e-05</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>MO06CUX03 Apertura</t>
+          <t>TR02CUX13 Partida de defunción SD</t>
         </is>
       </c>
       <c r="B439" s="5" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C439" s="6" t="n">
-        <v>5.960116717268731e-05</v>
+        <v>5.909607253563064e-05</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>TR02CUX10 Confirmar trámite</t>
+          <t>SA16CUX01 Monóxido de carbono</t>
         </is>
       </c>
       <c r="B440" s="5" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C440" s="6" t="n">
-        <v>5.960116717268731e-05</v>
+        <v>5.859097789857397e-05</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>SA16CUX01 Monóxido de carbono</t>
+          <t>EM03CUX02 Apertura</t>
         </is>
       </c>
       <c r="B441" s="5" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C441" s="6" t="n">
-        <v>5.859097789857397e-05</v>
+        <v>5.758078862446062e-05</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>EM03CUX02 Apertura</t>
+          <t>MO06CUX01 Apertura</t>
         </is>
       </c>
       <c r="B442" s="5" t="n">
@@ -6203,7 +6203,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>MO06CUX01 Apertura</t>
+          <t>INN01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B443" s="5" t="n">
@@ -6216,27 +6216,27 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>INN01CUX01 Apertura</t>
+          <t>TR04CUX08 Asiento de la defunción en la libreta de matrimonio</t>
         </is>
       </c>
       <c r="B444" s="5" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C444" s="6" t="n">
-        <v>5.657059935034727e-05</v>
+        <v>5.60655047132906e-05</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>TR04CUX08 Asiento de la defunción en la libreta de matrimonio</t>
+          <t>CIU05CUX03 La Boca</t>
         </is>
       </c>
       <c r="B445" s="5" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C445" s="6" t="n">
-        <v>5.60655047132906e-05</v>
+        <v>5.556041007623393e-05</v>
       </c>
     </row>
     <row r="446">
@@ -6268,7 +6268,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>CU02CUX01 Complejo Teatral</t>
+          <t>TR03CUX08 Apertura</t>
         </is>
       </c>
       <c r="B448" s="5" t="n">
@@ -6281,20 +6281,20 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>DDHH01CUX01 Apertura</t>
+          <t>MO04CUX08 Mapa Interactivo</t>
         </is>
       </c>
       <c r="B449" s="5" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C449" s="6" t="n">
-        <v>5.404512616506392e-05</v>
+        <v>5.354003152800725e-05</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>MO04CUX08 Mapa Interactivo</t>
+          <t>TR01CUX15 Apertura</t>
         </is>
       </c>
       <c r="B450" s="5" t="n">
@@ -6307,27 +6307,27 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>TR01CUX15 Apertura</t>
+          <t xml:space="preserve">TR04CUX32  Errores en pasaporte </t>
         </is>
       </c>
       <c r="B451" s="5" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C451" s="6" t="n">
-        <v>5.354003152800725e-05</v>
+        <v>5.303493689095057e-05</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>EDU04CUX19 Tengo una consulta</t>
+          <t>CU02CUX01 Complejo Teatral</t>
         </is>
       </c>
       <c r="B452" s="5" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C452" s="6" t="n">
-        <v>5.354003152800725e-05</v>
+        <v>5.303493689095057e-05</v>
       </c>
     </row>
     <row r="453">
@@ -6346,7 +6346,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t xml:space="preserve">TR04CUX32  Errores en pasaporte </t>
+          <t>Contingencia - ABRIL 2025</t>
         </is>
       </c>
       <c r="B454" s="5" t="n">
@@ -6359,7 +6359,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Contingencia - ABRIL 2025</t>
+          <t>DDHH01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B455" s="5" t="n">
@@ -6398,59 +6398,59 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>AM02CUX01 Apertura</t>
+          <t>EDU04CUX19 Tengo una consulta</t>
         </is>
       </c>
       <c r="B458" s="5" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C458" s="6" t="n">
-        <v>5.151965297978056e-05</v>
+        <v>5.202474761683723e-05</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>MO04CUX10 Apertura</t>
+          <t>AM02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B459" s="5" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C459" s="6" t="n">
-        <v>5.050946370566721e-05</v>
+        <v>5.151965297978056e-05</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>TR03CUX08 Apertura</t>
+          <t>MO04CUX10 Apertura</t>
         </is>
       </c>
       <c r="B460" s="5" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C460" s="6" t="n">
-        <v>4.949927443155387e-05</v>
+        <v>5.050946370566721e-05</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>MO10CUX06 Apertura</t>
+          <t>AC01CUX02 Gobierno Nacional</t>
         </is>
       </c>
       <c r="B461" s="5" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C461" s="6" t="n">
-        <v>4.949927443155387e-05</v>
+        <v>4.899417979449719e-05</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>AC01CUX02 Gobierno Nacional</t>
+          <t>MO10CUX06 Apertura</t>
         </is>
       </c>
       <c r="B462" s="5" t="n">
@@ -6476,20 +6476,20 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>ED04CUX17 Apertura</t>
+          <t>CU01CUX05 Apertura</t>
         </is>
       </c>
       <c r="B464" s="5" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C464" s="6" t="n">
-        <v>4.798399052038385e-05</v>
+        <v>4.747889588332718e-05</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>CU01CUX05 Apertura</t>
+          <t>ED04CUX17 Apertura</t>
         </is>
       </c>
       <c r="B465" s="5" t="n">
@@ -6528,14 +6528,14 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>DE05CUX02 Dónde se hacen</t>
+          <t>Deficiencias en la gestión</t>
         </is>
       </c>
       <c r="B468" s="5" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C468" s="6" t="n">
-        <v>4.646870660921384e-05</v>
+        <v>4.495342269804382e-05</v>
       </c>
     </row>
     <row r="469">
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="B469" s="5" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C469" s="6" t="n">
-        <v>4.545851733510049e-05</v>
+        <v>4.495342269804382e-05</v>
       </c>
     </row>
     <row r="470">
@@ -6580,20 +6580,20 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Deficiencias en la gestión</t>
+          <t>CU08CUX06 Festival urbano BA</t>
         </is>
       </c>
       <c r="B472" s="5" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C472" s="6" t="n">
-        <v>4.495342269804382e-05</v>
+        <v>4.444832806098715e-05</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>CU08CUX06 Festival urbano BA</t>
+          <t>EM04CUX02 Mujer Emprendedora</t>
         </is>
       </c>
       <c r="B473" s="5" t="n">
@@ -6606,14 +6606,14 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>EM04CUX02 Mujer Emprendedora</t>
+          <t>CU01CUX02 MALBA</t>
         </is>
       </c>
       <c r="B474" s="5" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C474" s="6" t="n">
-        <v>4.444832806098715e-05</v>
+        <v>4.394323342393048e-05</v>
       </c>
     </row>
     <row r="475">
@@ -6632,7 +6632,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>CIU05CUX01 Autonomía</t>
+          <t>Final | Búsqueda de Farmacias</t>
         </is>
       </c>
       <c r="B476" s="5" t="n">
@@ -6645,7 +6645,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Final | Búsqueda de Farmacias</t>
+          <t>DDHH03CUX04 Apertura</t>
         </is>
       </c>
       <c r="B477" s="5" t="n">
@@ -6658,332 +6658,332 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>DDHH03CUX04 Apertura</t>
+          <t>AM03CUX05 Superapertura</t>
         </is>
       </c>
       <c r="B478" s="5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C478" s="6" t="n">
-        <v>4.343813878687381e-05</v>
+        <v>4.293304414981713e-05</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>CU01CUX02 MALBA</t>
+          <t>Mensaje inicial</t>
         </is>
       </c>
       <c r="B479" s="5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C479" s="6" t="n">
-        <v>4.293304414981713e-05</v>
+        <v>4.242794951276046e-05</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>AM03CUX05 Superapertura</t>
+          <t xml:space="preserve">NI01CUX05 Boticuentos </t>
         </is>
       </c>
       <c r="B480" s="5" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C480" s="6" t="n">
-        <v>4.293304414981713e-05</v>
+        <v>4.192285487570378e-05</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Mensaje inicial</t>
+          <t>TU03CUX10 Apertura</t>
         </is>
       </c>
       <c r="B481" s="5" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C481" s="6" t="n">
-        <v>4.242794951276046e-05</v>
+        <v>4.192285487570378e-05</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>TR04CUX32  Apertura</t>
+          <t>CIU05CUX01 Autonomía</t>
         </is>
       </c>
       <c r="B482" s="5" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C482" s="6" t="n">
-        <v>4.242794951276046e-05</v>
+        <v>4.141776023864711e-05</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>TU03CUX10 Apertura</t>
+          <t>MO10CUX01 Apertura</t>
         </is>
       </c>
       <c r="B483" s="5" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C483" s="6" t="n">
-        <v>4.192285487570378e-05</v>
+        <v>4.040757096453377e-05</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t xml:space="preserve">NI01CUX05 Boticuentos </t>
+          <t xml:space="preserve"> TR04CUX31 Apertura</t>
         </is>
       </c>
       <c r="B484" s="5" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C484" s="6" t="n">
-        <v>4.192285487570378e-05</v>
+        <v>3.939738169042042e-05</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>SA11CUXO1 Plan de vacunación</t>
+          <t>TR04CUX31 Cómo lo hago</t>
         </is>
       </c>
       <c r="B485" s="5" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C485" s="6" t="n">
-        <v>3.939738169042042e-05</v>
+        <v>3.838719241630708e-05</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>MO10CUX01 Apertura</t>
+          <t>DEC03CUX01 Apertura</t>
         </is>
       </c>
       <c r="B486" s="5" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C486" s="6" t="n">
-        <v>3.939738169042042e-05</v>
+        <v>3.838719241630708e-05</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TR04CUX31 Apertura</t>
+          <t xml:space="preserve">Qué necesito | Certificado de residencia precaria </t>
         </is>
       </c>
       <c r="B487" s="5" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C487" s="6" t="n">
-        <v>3.939738169042042e-05</v>
+        <v>3.788209777925041e-05</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>SUA01CUX27 Pedido de dirección</t>
+          <t>El usuario ha enviado una ubicación</t>
         </is>
       </c>
       <c r="B488" s="5" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C488" s="6" t="n">
-        <v>3.939738169042042e-05</v>
+        <v>3.788209777925041e-05</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>DEC03CUX01 Apertura</t>
+          <t>TU03CUX09 Apertura</t>
         </is>
       </c>
       <c r="B489" s="5" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C489" s="6" t="n">
-        <v>3.838719241630708e-05</v>
+        <v>3.737700314219374e-05</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>El usuario ha enviado una ubicación</t>
+          <t>SUA01CUX00 Árboles</t>
         </is>
       </c>
       <c r="B490" s="5" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C490" s="6" t="n">
-        <v>3.788209777925041e-05</v>
+        <v>3.737700314219374e-05</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qué necesito | Certificado de residencia precaria </t>
+          <t>Registro de artistas callejeros (Apertura)</t>
         </is>
       </c>
       <c r="B491" s="5" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C491" s="6" t="n">
-        <v>3.788209777925041e-05</v>
+        <v>3.687190850513707e-05</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Registro de artistas callejeros (Apertura)</t>
+          <t>¿Algo más? |  Buscar comunas</t>
         </is>
       </c>
       <c r="B492" s="5" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C492" s="6" t="n">
-        <v>3.788209777925041e-05</v>
+        <v>3.63668138680804e-05</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>TR04CUX31 Cómo lo hago</t>
+          <t>SE01CUX04 Apertura</t>
         </is>
       </c>
       <c r="B493" s="5" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C493" s="6" t="n">
-        <v>3.737700314219374e-05</v>
+        <v>3.63668138680804e-05</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>SUA01CUX00 Árboles</t>
+          <t>Comuna Encontrada | Buscar comunas</t>
         </is>
       </c>
       <c r="B494" s="5" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C494" s="6" t="n">
-        <v>3.737700314219374e-05</v>
+        <v>3.63668138680804e-05</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Comuna Encontrada | Buscar comunas</t>
+          <t>DE05CUX02 Dónde se hacen</t>
         </is>
       </c>
       <c r="B495" s="5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C495" s="6" t="n">
-        <v>3.63668138680804e-05</v>
+        <v>3.586171923102372e-05</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>SE01CUX04 Apertura</t>
+          <t>TR03CUX17 Reserva de espacio para estacionamiento de vehículos de personas con discapacidad</t>
         </is>
       </c>
       <c r="B496" s="5" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C496" s="6" t="n">
-        <v>3.63668138680804e-05</v>
+        <v>3.485152995691038e-05</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>¿Algo más? |  Buscar comunas</t>
+          <t>AM04CUX04 Apertura</t>
         </is>
       </c>
       <c r="B497" s="5" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C497" s="6" t="n">
-        <v>3.63668138680804e-05</v>
+        <v>3.485152995691038e-05</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>AM04CUX04 Apertura</t>
+          <t>ED04CUX17 Cómo funciona</t>
         </is>
       </c>
       <c r="B498" s="5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C498" s="6" t="n">
-        <v>3.535662459396705e-05</v>
+        <v>3.485152995691038e-05</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>TU03CUX09 Apertura</t>
+          <t>DH05CUX01 Adicción al juego</t>
         </is>
       </c>
       <c r="B499" s="5" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C499" s="6" t="n">
-        <v>3.485152995691038e-05</v>
+        <v>3.43464353198537e-05</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>TR03CUX17 Reserva de espacio para estacionamiento de vehículos de personas con discapacidad</t>
+          <t>DH11CUX02 Chat por whatsapp</t>
         </is>
       </c>
       <c r="B500" s="5" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C500" s="6" t="n">
-        <v>3.485152995691038e-05</v>
+        <v>3.384134068279703e-05</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>ED04CUX17 Cómo funciona</t>
+          <t>CIU05CUX11 Apertura con pedido de barrio</t>
         </is>
       </c>
       <c r="B501" s="5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C501" s="6" t="n">
-        <v>3.43464353198537e-05</v>
+        <v>3.384134068279703e-05</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>DH05CUX01 Adicción al juego</t>
+          <t>CO12CUX02 Temporal en BA</t>
         </is>
       </c>
       <c r="B502" s="5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C502" s="6" t="n">
-        <v>3.43464353198537e-05</v>
+        <v>3.384134068279703e-05</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>CO12CUX02 Temporal en BA</t>
+          <t xml:space="preserve">Más información | Certificado de residencia precaria </t>
         </is>
       </c>
       <c r="B503" s="5" t="n">
@@ -6996,20 +6996,20 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t xml:space="preserve">Más información | Certificado de residencia precaria </t>
+          <t>Imágenes</t>
         </is>
       </c>
       <c r="B504" s="5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C504" s="6" t="n">
-        <v>3.384134068279703e-05</v>
+        <v>3.333624604574036e-05</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Imágenes</t>
+          <t>CU09CUX03 Apertura</t>
         </is>
       </c>
       <c r="B505" s="5" t="n">
@@ -7022,14 +7022,14 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>DH07CUX01 Apertura</t>
+          <t>CO08CUX07 Apertura</t>
         </is>
       </c>
       <c r="B506" s="5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C506" s="6" t="n">
-        <v>3.333624604574036e-05</v>
+        <v>3.283115140868369e-05</v>
       </c>
     </row>
     <row r="507">
@@ -7039,172 +7039,172 @@
         </is>
       </c>
       <c r="B507" s="5" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C507" s="6" t="n">
-        <v>3.333624604574036e-05</v>
+        <v>3.232605677162701e-05</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>CU01CUX02 Apertura</t>
+          <t xml:space="preserve">DH05CUX01 Apertura </t>
         </is>
       </c>
       <c r="B508" s="5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C508" s="6" t="n">
-        <v>3.283115140868369e-05</v>
+        <v>3.182096213457034e-05</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>DH11CUX02 Chat por whatsapp</t>
+          <t>CO08CUX06 Apertura</t>
         </is>
       </c>
       <c r="B509" s="5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C509" s="6" t="n">
-        <v>3.283115140868369e-05</v>
+        <v>3.182096213457034e-05</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>CU09CUX03 Apertura</t>
+          <t>JU03CUX01 Apertura</t>
         </is>
       </c>
       <c r="B510" s="5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C510" s="6" t="n">
-        <v>3.232605677162701e-05</v>
+        <v>3.182096213457034e-05</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>CO08CUX07 Apertura</t>
+          <t>DH07CUX01 Apertura</t>
         </is>
       </c>
       <c r="B511" s="5" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C511" s="6" t="n">
-        <v>3.232605677162701e-05</v>
+        <v>3.131586749751367e-05</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>CIU05CUX11 Apertura con pedido de barrio</t>
+          <t>DDHH03CUX02 Apertura</t>
         </is>
       </c>
       <c r="B512" s="5" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C512" s="6" t="n">
-        <v>3.232605677162701e-05</v>
+        <v>3.131586749751367e-05</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>JU03CUX01 Apertura</t>
+          <t xml:space="preserve">CU08CUX07 Apertura de contingencia </t>
         </is>
       </c>
       <c r="B513" s="5" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C513" s="6" t="n">
-        <v>3.232605677162701e-05</v>
+        <v>3.030567822340033e-05</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>CO08CUX06 Apertura</t>
+          <t>SE01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B514" s="5" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C514" s="6" t="n">
-        <v>3.182096213457034e-05</v>
+        <v>3.030567822340033e-05</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>DDHH03CUX02 Apertura</t>
+          <t>SUA01CUX27 Pedido de dirección</t>
         </is>
       </c>
       <c r="B515" s="5" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C515" s="6" t="n">
-        <v>3.182096213457034e-05</v>
+        <v>3.030567822340033e-05</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t xml:space="preserve">CU08CUX07 Apertura de contingencia </t>
+          <t>AM03CUX04 Apertura Ambiente</t>
         </is>
       </c>
       <c r="B516" s="5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C516" s="6" t="n">
-        <v>3.030567822340033e-05</v>
+        <v>2.929548894928698e-05</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>SE01CUX01 Apertura</t>
+          <t>CU01CUX02 Apertura</t>
         </is>
       </c>
       <c r="B517" s="5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C517" s="6" t="n">
-        <v>3.030567822340033e-05</v>
+        <v>2.929548894928698e-05</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t xml:space="preserve">DH05CUX01 Apertura </t>
+          <t xml:space="preserve">Cómo lo renuevo | Certificado de residencia precaria </t>
         </is>
       </c>
       <c r="B518" s="5" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C518" s="6" t="n">
-        <v>2.980058358634365e-05</v>
+        <v>2.828529967517364e-05</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>AM03CUX04 Apertura Ambiente</t>
+          <t>TU03CUX05 Apertura</t>
         </is>
       </c>
       <c r="B519" s="5" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C519" s="6" t="n">
-        <v>2.980058358634365e-05</v>
+        <v>2.828529967517364e-05</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>GA03CUX03 Apertura</t>
+          <t>EDU04CUX02 Apertura</t>
         </is>
       </c>
       <c r="B520" s="5" t="n">
@@ -7230,27 +7230,27 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>EDU04CUX02 Apertura</t>
+          <t>DH03CUX01 Subapertura estática</t>
         </is>
       </c>
       <c r="B522" s="5" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C522" s="6" t="n">
-        <v>2.828529967517364e-05</v>
+        <v>2.778020503811697e-05</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>TU03CUX05 Apertura</t>
+          <t>Derivación Becas Alimentarias - Fuera de horario de atención</t>
         </is>
       </c>
       <c r="B523" s="5" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C523" s="6" t="n">
-        <v>2.828529967517364e-05</v>
+        <v>2.778020503811697e-05</v>
       </c>
     </row>
     <row r="524">
@@ -7269,111 +7269,111 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>DH03CUX01 Subapertura estática</t>
+          <t xml:space="preserve">Cómo lo tramito | Certificado de residencia precaria </t>
         </is>
       </c>
       <c r="B525" s="5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C525" s="6" t="n">
-        <v>2.778020503811697e-05</v>
+        <v>2.72751104010603e-05</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Derivación Becas Alimentarias - ✅ Auxiliar disponible</t>
+          <t>GA03CUX03 Apertura</t>
         </is>
       </c>
       <c r="B526" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C526" s="6" t="n">
-        <v>2.677001576400362e-05</v>
+        <v>2.72751104010603e-05</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>TR01CUX18  Apertura</t>
+          <t>TR01CUX03  Apertura</t>
         </is>
       </c>
       <c r="B527" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C527" s="6" t="n">
-        <v>2.626492112694695e-05</v>
+        <v>2.677001576400362e-05</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>TU03CUX03 Apertura</t>
+          <t>CIU05CUX07 Apertura</t>
         </is>
       </c>
       <c r="B528" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C528" s="6" t="n">
-        <v>2.626492112694695e-05</v>
+        <v>2.677001576400362e-05</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>CIU05CUX07 Apertura</t>
+          <t>Derivación Becas Alimentarias - ✅ Auxiliar disponible</t>
         </is>
       </c>
       <c r="B529" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C529" s="6" t="n">
-        <v>2.626492112694695e-05</v>
+        <v>2.677001576400362e-05</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Derivación Becas Alimentarias - Fuera de horario de atención</t>
+          <t>TR03CUX08 Habilitaciones</t>
         </is>
       </c>
       <c r="B530" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C530" s="6" t="n">
-        <v>2.626492112694695e-05</v>
+        <v>2.677001576400362e-05</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>TR01CUX03  Apertura</t>
+          <t>TU03CUX03 Apertura</t>
         </is>
       </c>
       <c r="B531" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C531" s="6" t="n">
-        <v>2.575982648989028e-05</v>
+        <v>2.626492112694695e-05</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>TR03CUX08 Habilitaciones</t>
+          <t>TR01CUX18  Apertura</t>
         </is>
       </c>
       <c r="B532" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C532" s="6" t="n">
-        <v>2.575982648989028e-05</v>
+        <v>2.626492112694695e-05</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cómo lo tramito | Certificado de residencia precaria </t>
+          <t>DH11CUX04 Apertura</t>
         </is>
       </c>
       <c r="B533" s="5" t="n">
@@ -7386,7 +7386,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>DH11CUX04 Apertura</t>
+          <t>Derivación a Boti</t>
         </is>
       </c>
       <c r="B534" s="5" t="n">
@@ -7412,7 +7412,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Derivación a Boti</t>
+          <t>DH02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B536" s="5" t="n">
@@ -7425,72 +7425,72 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cómo lo renuevo | Certificado de residencia precaria </t>
+          <t>CU01CUX15 Apertura Experiencia Interactiva</t>
         </is>
       </c>
       <c r="B537" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C537" s="6" t="n">
-        <v>2.474963721577693e-05</v>
+        <v>2.525473185283361e-05</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>CU02CUX01 Apertura</t>
+          <t>OB05CUX01 Número de expediente</t>
         </is>
       </c>
       <c r="B538" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C538" s="6" t="n">
-        <v>2.474963721577693e-05</v>
+        <v>2.525473185283361e-05</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>CU01CUX15 Apertura Experiencia Interactiva</t>
+          <t>CU02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B539" s="5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C539" s="6" t="n">
-        <v>2.474963721577693e-05</v>
+        <v>2.424454257872026e-05</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>TR03CUX25 Terminales de pago</t>
+          <t>JU02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B540" s="5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C540" s="6" t="n">
-        <v>2.424454257872026e-05</v>
+        <v>2.373944794166359e-05</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>DH02CUX01 Apertura</t>
+          <t>BX02CUX01 Pregunta 1</t>
         </is>
       </c>
       <c r="B541" s="5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C541" s="6" t="n">
-        <v>2.424454257872026e-05</v>
+        <v>2.373944794166359e-05</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>JU02CUX01 Apertura</t>
+          <t>TUR01CUX12 Preguntar género</t>
         </is>
       </c>
       <c r="B542" s="5" t="n">
@@ -7503,20 +7503,20 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>OB05CUX01 Número de expediente</t>
+          <t>CU04CUX19 Apertura de contingencia</t>
         </is>
       </c>
       <c r="B543" s="5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C543" s="6" t="n">
-        <v>2.373944794166359e-05</v>
+        <v>2.323435330460692e-05</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>CU04CUX19 Apertura de contingencia</t>
+          <t>Forms</t>
         </is>
       </c>
       <c r="B544" s="5" t="n">
@@ -7529,27 +7529,27 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>BX02CUX01 Pregunta 1</t>
+          <t>TR03CUX25 Terminales de pago</t>
         </is>
       </c>
       <c r="B545" s="5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C545" s="6" t="n">
-        <v>2.323435330460692e-05</v>
+        <v>2.272925866755024e-05</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Forms</t>
+          <t>Clausura obra o local</t>
         </is>
       </c>
       <c r="B546" s="5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C546" s="6" t="n">
-        <v>2.323435330460692e-05</v>
+        <v>2.272925866755024e-05</v>
       </c>
     </row>
     <row r="547">
@@ -7568,33 +7568,33 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Clausura obra o local</t>
+          <t>SA07CUX01 VIH</t>
         </is>
       </c>
       <c r="B548" s="5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C548" s="6" t="n">
-        <v>2.272925866755024e-05</v>
+        <v>2.222416403049357e-05</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>SA07CUX01 VIH</t>
+          <t>TR03CUX03 Subsidios</t>
         </is>
       </c>
       <c r="B549" s="5" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C549" s="6" t="n">
-        <v>2.222416403049357e-05</v>
+        <v>2.17190693934369e-05</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>TR03CUX03 Subsidios</t>
+          <t>CIU05CUX01 Apertura</t>
         </is>
       </c>
       <c r="B550" s="5" t="n">
@@ -7607,7 +7607,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>DDHH03CUX05 Apertura</t>
+          <t>Imagenes</t>
         </is>
       </c>
       <c r="B551" s="5" t="n">
@@ -7620,7 +7620,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>SE01CUX06 Apertura</t>
+          <t>DDHH03CUX05 Apertura</t>
         </is>
       </c>
       <c r="B552" s="5" t="n">
@@ -7633,7 +7633,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Imagenes</t>
+          <t>SE01CUX06 Apertura</t>
         </is>
       </c>
       <c r="B553" s="5" t="n">
@@ -7646,7 +7646,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>MO05CUX03 Apertura</t>
+          <t>Desambiguador deudas</t>
         </is>
       </c>
       <c r="B554" s="5" t="n">
@@ -7659,53 +7659,53 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>CIU05CUX01 Apertura</t>
+          <t>CU01CUX02 Colón Fábrica</t>
         </is>
       </c>
       <c r="B555" s="5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C555" s="6" t="n">
-        <v>1.969869084521021e-05</v>
+        <v>1.919359620815354e-05</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Desambiguador deudas</t>
+          <t>TU01CUX15 Apertura</t>
         </is>
       </c>
       <c r="B556" s="5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C556" s="6" t="n">
-        <v>1.969869084521021e-05</v>
+        <v>1.919359620815354e-05</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Flow fulfilled of "Wsp"</t>
+          <t>AM04CUX06 Apertura</t>
         </is>
       </c>
       <c r="B557" s="5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C557" s="6" t="n">
-        <v>1.969869084521021e-05</v>
+        <v>1.919359620815354e-05</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>TR02CUX12 Qué necesito</t>
+          <t>MO10CUX07 Apertura</t>
         </is>
       </c>
       <c r="B558" s="5" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C558" s="6" t="n">
-        <v>1.969869084521021e-05</v>
+        <v>1.868850157109687e-05</v>
       </c>
     </row>
     <row r="559">
@@ -7715,101 +7715,101 @@
         </is>
       </c>
       <c r="B559" s="5" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C559" s="6" t="n">
-        <v>1.969869084521021e-05</v>
+        <v>1.868850157109687e-05</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>AM04CUX06 Apertura</t>
+          <t>SA08CUX01 Apertura</t>
         </is>
       </c>
       <c r="B560" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C560" s="6" t="n">
-        <v>1.919359620815354e-05</v>
+        <v>1.868850157109687e-05</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>TR03CUX08 Seguridad alimentaria</t>
+          <t>Flow fulfilled of "Wsp"</t>
         </is>
       </c>
       <c r="B561" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C561" s="6" t="n">
-        <v>1.919359620815354e-05</v>
+        <v>1.868850157109687e-05</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>TU01CUX15 Apertura</t>
+          <t>Feedback a humano - Unificado</t>
         </is>
       </c>
       <c r="B562" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C562" s="6" t="n">
-        <v>1.919359620815354e-05</v>
+        <v>1.868850157109687e-05</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>MO10CUX07 Apertura</t>
+          <t>MO05CUX03 Apertura</t>
         </is>
       </c>
       <c r="B563" s="5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C563" s="6" t="n">
-        <v>1.868850157109687e-05</v>
+        <v>1.81834069340402e-05</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Feedback a humano - Unificado</t>
+          <t>Dónde hacerlo | Certificación de firmas</t>
         </is>
       </c>
       <c r="B564" s="5" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C564" s="6" t="n">
-        <v>1.868850157109687e-05</v>
+        <v>1.767831229698352e-05</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>CU10CUX02 Esquina Mafalda</t>
+          <t>Servicios sociales</t>
         </is>
       </c>
       <c r="B565" s="5" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C565" s="6" t="n">
-        <v>1.868850157109687e-05</v>
+        <v>1.767831229698352e-05</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>SA08CUX01 Apertura</t>
+          <t>CU10CUX02 Esquina Mafalda</t>
         </is>
       </c>
       <c r="B566" s="5" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C566" s="6" t="n">
-        <v>1.868850157109687e-05</v>
+        <v>1.767831229698352e-05</v>
       </c>
     </row>
     <row r="567">
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="B567" s="5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C567" s="6" t="n">
-        <v>1.81834069340402e-05</v>
+        <v>1.767831229698352e-05</v>
       </c>
     </row>
     <row r="568">
@@ -7841,7 +7841,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Servicios sociales</t>
+          <t>Licencias Boti</t>
         </is>
       </c>
       <c r="B569" s="5" t="n">
@@ -7854,20 +7854,20 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Licencias Boti</t>
+          <t>TR02CUX12 Qué necesito</t>
         </is>
       </c>
       <c r="B570" s="5" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C570" s="6" t="n">
-        <v>1.767831229698352e-05</v>
+        <v>1.666812302287018e-05</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>CU01CUX02 Colón Fábrica</t>
+          <t>CU08CUX02 Cuidados del calor</t>
         </is>
       </c>
       <c r="B571" s="5" t="n">
@@ -7880,14 +7880,14 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>CU08CUX02 Cuidados del calor</t>
+          <t>CU08CUX01  Apertura de contingencia II</t>
         </is>
       </c>
       <c r="B572" s="5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C572" s="6" t="n">
-        <v>1.666812302287018e-05</v>
+        <v>1.616302838581351e-05</v>
       </c>
     </row>
     <row r="573">
@@ -7906,33 +7906,33 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>CU08CUX01  Apertura de contingencia II</t>
+          <t>EDU04CUX23 Apertura</t>
         </is>
       </c>
       <c r="B574" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C574" s="6" t="n">
-        <v>1.616302838581351e-05</v>
+        <v>1.565793374875684e-05</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Dónde hacerlo | Certificación de firmas</t>
+          <t>Webchat Identificar Customer</t>
         </is>
       </c>
       <c r="B575" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C575" s="6" t="n">
-        <v>1.616302838581351e-05</v>
+        <v>1.565793374875684e-05</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>CIU02CUX00 Superapertura</t>
+          <t>DH011CUX02 Presencial</t>
         </is>
       </c>
       <c r="B576" s="5" t="n">
@@ -7945,7 +7945,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>DH011CUX02 Presencial</t>
+          <t>CIU02CUX00 Superapertura</t>
         </is>
       </c>
       <c r="B577" s="5" t="n">
@@ -7958,46 +7958,46 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>EDU04CUX23 Apertura</t>
+          <t>TR04CUX16 Apertura</t>
         </is>
       </c>
       <c r="B578" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C578" s="6" t="n">
-        <v>1.565793374875684e-05</v>
+        <v>1.464774447464349e-05</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Webchat Identificar Customer</t>
+          <t>SA18CUX01 Apertura</t>
         </is>
       </c>
       <c r="B579" s="5" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C579" s="6" t="n">
-        <v>1.565793374875684e-05</v>
+        <v>1.414264983758682e-05</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>CU10CUX02 Clemente</t>
+          <t>SUA01CUX20 Apertura</t>
         </is>
       </c>
       <c r="B580" s="5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C580" s="6" t="n">
-        <v>1.464774447464349e-05</v>
+        <v>1.414264983758682e-05</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Hacer una consulta - Trámites Rúbrica</t>
+          <t>Carrusel</t>
         </is>
       </c>
       <c r="B581" s="5" t="n">
@@ -8010,7 +8010,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>TR04CUX16 Apertura</t>
+          <t>TR03CUX08 Seguridad alimentaria</t>
         </is>
       </c>
       <c r="B582" s="5" t="n">
@@ -8023,7 +8023,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>Carrusel</t>
+          <t>Hacer una consulta - Trámites Rúbrica</t>
         </is>
       </c>
       <c r="B583" s="5" t="n">
@@ -8036,7 +8036,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>SA18CUX01 Apertura</t>
+          <t>MO05CUX03 Cómo hacerlo</t>
         </is>
       </c>
       <c r="B584" s="5" t="n">
@@ -8049,20 +8049,20 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>SUA01CUX20 Apertura</t>
+          <t>CU10CUX02 Clemente</t>
         </is>
       </c>
       <c r="B585" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C585" s="6" t="n">
-        <v>1.363755520053015e-05</v>
+        <v>1.414264983758682e-05</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>MO09CUX04 Apertura</t>
+          <t>SA01CUX06  Apertura corta</t>
         </is>
       </c>
       <c r="B586" s="5" t="n">
@@ -8075,7 +8075,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>SA01CUX06  Apertura corta</t>
+          <t>MO09CUX04 Apertura</t>
         </is>
       </c>
       <c r="B587" s="5" t="n">
@@ -8088,7 +8088,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>TUR01CUX12 Pedir tipo de documento</t>
+          <t>Ubicación</t>
         </is>
       </c>
       <c r="B588" s="5" t="n">
@@ -8101,7 +8101,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>Ubicación</t>
+          <t>TUR01CUX12 Pedir tipo de documento</t>
         </is>
       </c>
       <c r="B589" s="5" t="n">
@@ -8114,20 +8114,20 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>MO05CUX03 Cómo hacerlo</t>
+          <t>TR05CUX04 No figura en el registro</t>
         </is>
       </c>
       <c r="B590" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C590" s="6" t="n">
-        <v>1.26273659264168e-05</v>
+        <v>1.313246056347347e-05</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>Coronavirus y gente de más de 70 (Apertura)  &gt; Hacer las compras * Apertura</t>
+          <t>Realizar búsqueda de Código Postal por domicilio</t>
         </is>
       </c>
       <c r="B591" s="5" t="n">
@@ -8140,20 +8140,20 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>TR03CUX27  Apertura</t>
+          <t>Coronavirus y gente de más de 70 (Apertura)  &gt; Hacer las compras * Apertura</t>
         </is>
       </c>
       <c r="B592" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C592" s="6" t="n">
-        <v>1.212227128936013e-05</v>
+        <v>1.26273659264168e-05</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>AM03CUX04 Áreas Protegidas</t>
+          <t>TR03CUX27  Apertura</t>
         </is>
       </c>
       <c r="B593" s="5" t="n">
@@ -8166,7 +8166,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>Realizar búsqueda de Código Postal por domicilio</t>
+          <t>AM03CUX04 Áreas Protegidas</t>
         </is>
       </c>
       <c r="B594" s="5" t="n">
@@ -8179,7 +8179,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>INN10CUX09 CA Ejecutar PI</t>
+          <t>INN10CUX13 - Vuelta</t>
         </is>
       </c>
       <c r="B595" s="5" t="n">
@@ -8192,7 +8192,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>INN10CUX13 - Vuelta</t>
+          <t>SUA01CUX27 Dónde ubicar la luminaria</t>
         </is>
       </c>
       <c r="B596" s="5" t="n">
@@ -8231,7 +8231,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>CU01CUX16 Apertura (post-evento)</t>
+          <t>TU03CUX15 Apertura</t>
         </is>
       </c>
       <c r="B599" s="5" t="n">
@@ -8244,7 +8244,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>TR05CUX04 No figura en el registro</t>
+          <t>CU01CUX16 Apertura (post-evento)</t>
         </is>
       </c>
       <c r="B600" s="5" t="n">
@@ -8257,27 +8257,27 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>TU03CUX15 Apertura</t>
+          <t>DH11CUX08 Apertura</t>
         </is>
       </c>
       <c r="B601" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C601" s="6" t="n">
-        <v>1.111208201524679e-05</v>
+        <v>1.060698737819011e-05</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>Derivación Becas Alimentarias - ⛔ Auxiliar no disponible</t>
+          <t>Código Postal por ubicación actual 2</t>
         </is>
       </c>
       <c r="B602" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C602" s="6" t="n">
-        <v>1.111208201524679e-05</v>
+        <v>1.060698737819011e-05</v>
       </c>
     </row>
     <row r="603">
@@ -8296,7 +8296,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>Código Postal por ubicación actual 2</t>
+          <t xml:space="preserve">SE01CUX06 Qué puedo denunciar </t>
         </is>
       </c>
       <c r="B604" s="5" t="n">
@@ -8309,46 +8309,46 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>DH11CUX08 Apertura</t>
+          <t>SA01CUX07 - Formulario para declarar vacuna</t>
         </is>
       </c>
       <c r="B605" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C605" s="6" t="n">
-        <v>1.010189274113344e-05</v>
+        <v>9.59679810407677e-06</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t xml:space="preserve">SE01CUX06 Qué puedo denunciar </t>
+          <t>AGC01CUX02 Libro Digital</t>
         </is>
       </c>
       <c r="B606" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C606" s="6" t="n">
-        <v>1.010189274113344e-05</v>
+        <v>9.59679810407677e-06</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>SUA01CUX26 Apertura</t>
+          <t xml:space="preserve">Requisitos | Disolución de Unión Civil / Convivencial </t>
         </is>
       </c>
       <c r="B607" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C607" s="6" t="n">
-        <v>1.010189274113344e-05</v>
+        <v>9.59679810407677e-06</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>TU01CUX02 Turismo en Boti</t>
+          <t>SUA01CUX26 Apertura</t>
         </is>
       </c>
       <c r="B608" s="5" t="n">
@@ -8361,46 +8361,46 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>SA01CUX07 - Formulario para declarar vacuna</t>
+          <t>TU01CUX02 Turismo en Boti</t>
         </is>
       </c>
       <c r="B609" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C609" s="6" t="n">
-        <v>9.59679810407677e-06</v>
+        <v>9.091703467020099e-06</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>AGC01CUX02 Libro Digital</t>
+          <t>TR03CUX03 Apertura</t>
         </is>
       </c>
       <c r="B610" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C610" s="6" t="n">
-        <v>9.59679810407677e-06</v>
+        <v>9.091703467020099e-06</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t xml:space="preserve">Requisitos | Disolución de Unión Civil / Convivencial </t>
+          <t>CU10CUX02 Apertura Mafalda</t>
         </is>
       </c>
       <c r="B611" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C611" s="6" t="n">
-        <v>9.59679810407677e-06</v>
+        <v>9.091703467020099e-06</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>TR03CUX03 Apertura</t>
+          <t>AC02CUX04 SAME</t>
         </is>
       </c>
       <c r="B612" s="5" t="n">
@@ -8413,111 +8413,111 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>AC02CUX04 SAME</t>
+          <t>Llamá gratis al 144</t>
         </is>
       </c>
       <c r="B613" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C613" s="6" t="n">
-        <v>9.091703467020099e-06</v>
+        <v>8.586608829963426e-06</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>Llamá gratis al 144</t>
+          <t xml:space="preserve">EDU04CUX30 Adolescencia </t>
         </is>
       </c>
       <c r="B614" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C614" s="6" t="n">
-        <v>8.586608829963426e-06</v>
+        <v>8.081514192906753e-06</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDU04CUX30 Adolescencia </t>
+          <t>TR02CUX07 Apertura</t>
         </is>
       </c>
       <c r="B615" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C615" s="6" t="n">
-        <v>8.586608829963426e-06</v>
+        <v>8.081514192906753e-06</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>TR03CUX07 Apertura</t>
+          <t>Respuestas TXT Gen</t>
         </is>
       </c>
       <c r="B616" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C616" s="6" t="n">
-        <v>8.586608829963426e-06</v>
+        <v>8.081514192906753e-06</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>Respuestas TXT Gen</t>
+          <t>EP04CUX01 Apertura web</t>
         </is>
       </c>
       <c r="B617" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C617" s="6" t="n">
-        <v>8.081514192906753e-06</v>
+        <v>7.576419555850082e-06</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>MO06CUX03 Más de bicis en BA</t>
+          <t>Salir de la experiencia</t>
         </is>
       </c>
       <c r="B618" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C618" s="6" t="n">
-        <v>8.081514192906753e-06</v>
+        <v>7.576419555850082e-06</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>TR02CUX07 Apertura</t>
+          <t>Registro de Establecimientos Gastronómicos</t>
         </is>
       </c>
       <c r="B619" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C619" s="6" t="n">
-        <v>8.081514192906753e-06</v>
+        <v>7.576419555850082e-06</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>TUR01CUX03 Validar datos</t>
+          <t>MO06CUX03 Más de bicis en BA</t>
         </is>
       </c>
       <c r="B620" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C620" s="6" t="n">
-        <v>8.081514192906753e-06</v>
+        <v>7.576419555850082e-06</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>SA16CUX02 Quiero vacunarme</t>
+          <t>Costos del trámite | Disolución de Unión Civil / Convivencial</t>
         </is>
       </c>
       <c r="B621" s="5" t="n">
@@ -8530,7 +8530,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>Mitre -Viaductos-</t>
+          <t>BA Pyme</t>
         </is>
       </c>
       <c r="B622" s="5" t="n">
@@ -8543,7 +8543,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>BA Pyme</t>
+          <t>Mostrar Resultados | Ecobici</t>
         </is>
       </c>
       <c r="B623" s="5" t="n">
@@ -8556,7 +8556,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>Salir de la experiencia</t>
+          <t>Mitre -Viaductos-</t>
         </is>
       </c>
       <c r="B624" s="5" t="n">
@@ -8569,7 +8569,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>CU10CUX02 Apertura Mafalda</t>
+          <t>SA16CUX02 Quiero vacunarme</t>
         </is>
       </c>
       <c r="B625" s="5" t="n">
@@ -8582,20 +8582,20 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>Costos del trámite | Disolución de Unión Civil / Convivencial</t>
+          <t>Situación de calle</t>
         </is>
       </c>
       <c r="B626" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C626" s="6" t="n">
-        <v>7.576419555850082e-06</v>
+        <v>7.071324918793409e-06</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>EP04CUX01 Apertura sin registro contingencia</t>
+          <t>INN07CUX02 Apertura</t>
         </is>
       </c>
       <c r="B627" s="5" t="n">
@@ -8608,7 +8608,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>INN07CUX02 Apertura</t>
+          <t>TUR01CUX03 Validar datos</t>
         </is>
       </c>
       <c r="B628" s="5" t="n">
@@ -8621,7 +8621,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>Situación de calle</t>
+          <t>DH11CUX03 Apertura QR keywords</t>
         </is>
       </c>
       <c r="B629" s="5" t="n">
@@ -8634,14 +8634,14 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>Mostrar Resultados | Ecobici</t>
+          <t>CU04CUX16 Apertura contingencia</t>
         </is>
       </c>
       <c r="B630" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C630" s="6" t="n">
-        <v>7.071324918793409e-06</v>
+        <v>6.566230281736737e-06</v>
       </c>
     </row>
     <row r="631">
@@ -8660,111 +8660,111 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>ED03CUX05 Profesorados</t>
+          <t>EP04CUX01 Apertura sin registro contingencia</t>
         </is>
       </c>
       <c r="B632" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C632" s="6" t="n">
-        <v>6.566230281736737e-06</v>
+        <v>6.061135644680065e-06</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>CU01CUX14 Quiero ir</t>
+          <t>Qué necesito | Identificación Tardía</t>
         </is>
       </c>
       <c r="B633" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C633" s="6" t="n">
-        <v>6.566230281736737e-06</v>
+        <v>6.061135644680065e-06</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>DEC05CUX02 Apertura</t>
+          <t>EDU05CUX06 Otros profesorados</t>
         </is>
       </c>
       <c r="B634" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C634" s="6" t="n">
-        <v>6.566230281736737e-06</v>
+        <v>6.061135644680065e-06</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>Registro de Establecimientos Gastronómicos</t>
+          <t>TR03CUX05 Biblioteca Docente</t>
         </is>
       </c>
       <c r="B635" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C635" s="6" t="n">
-        <v>6.566230281736737e-06</v>
+        <v>6.061135644680065e-06</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>CU04CUX16 Apertura contingencia</t>
+          <t>EDU10CUX01 Info de contacto 2</t>
         </is>
       </c>
       <c r="B636" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C636" s="6" t="n">
-        <v>6.566230281736737e-06</v>
+        <v>6.061135644680065e-06</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>DH05CUX01 Hablar con alguien</t>
+          <t>San Martín -Viaductos-</t>
         </is>
       </c>
       <c r="B637" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C637" s="6" t="n">
-        <v>6.061135644680065e-06</v>
+        <v>5.556041007623393e-06</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>EDU10CUX01 Info de contacto 2</t>
+          <t>Derivación Becas Alimentarias - ⛔ Auxiliar no disponible</t>
         </is>
       </c>
       <c r="B638" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C638" s="6" t="n">
-        <v>6.061135644680065e-06</v>
+        <v>5.556041007623393e-06</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>TR03CUX05 Biblioteca Docente</t>
+          <t>CU01CUX07 Apertura</t>
         </is>
       </c>
       <c r="B639" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C639" s="6" t="n">
-        <v>6.061135644680065e-06</v>
+        <v>5.556041007623393e-06</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>San Martín -Viaductos-</t>
+          <t>Resolver Ubicación Domicilio | Baches</t>
         </is>
       </c>
       <c r="B640" s="5" t="n">
@@ -8777,7 +8777,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>TU03CUX09 Qué hay para hacer</t>
+          <t>CU10CUX02 Paseo de Historietas</t>
         </is>
       </c>
       <c r="B641" s="5" t="n">
@@ -8790,7 +8790,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>EP04CUX01 Apertura web</t>
+          <t xml:space="preserve">Antecedentes penales | Certificado de residencia precaria </t>
         </is>
       </c>
       <c r="B642" s="5" t="n">
@@ -8803,85 +8803,85 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>Cómo lo tramito | Identificación Tardía</t>
+          <t>CU02CUX01 Teatro San Martín</t>
         </is>
       </c>
       <c r="B643" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C643" s="6" t="n">
-        <v>5.556041007623393e-06</v>
+        <v>5.050946370566721e-06</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>CU10CUX02 Paseo de Historietas</t>
+          <t>SUA01CUX22 Apertura desratización en colegios</t>
         </is>
       </c>
       <c r="B644" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C644" s="6" t="n">
-        <v>5.556041007623393e-06</v>
+        <v>5.050946370566721e-06</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>Resolver Ubicación Domicilio | Baches</t>
+          <t>Suaci - Error de foto obligatoria</t>
         </is>
       </c>
       <c r="B645" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C645" s="6" t="n">
-        <v>5.556041007623393e-06</v>
+        <v>5.050946370566721e-06</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>CU01CUX07 Apertura</t>
+          <t>TR03CUX07 Apertura</t>
         </is>
       </c>
       <c r="B646" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C646" s="6" t="n">
-        <v>5.556041007623393e-06</v>
+        <v>5.050946370566721e-06</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>Qué necesito | Identificación Tardía</t>
+          <t>01. CIU02CUX01 - Comunas de la Ciudad</t>
         </is>
       </c>
       <c r="B647" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C647" s="6" t="n">
-        <v>5.556041007623393e-06</v>
+        <v>5.050946370566721e-06</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antecedentes penales | Certificado de residencia precaria </t>
+          <t>Hisopado * Apertura WEB</t>
         </is>
       </c>
       <c r="B648" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C648" s="6" t="n">
-        <v>5.556041007623393e-06</v>
+        <v>5.050946370566721e-06</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>01. CIU02CUX01 - Comunas de la Ciudad</t>
+          <t>TR03CUX06 Servicios de salud para la prevención de zoonosis</t>
         </is>
       </c>
       <c r="B649" s="5" t="n">
@@ -8894,7 +8894,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>CU10CUX02 La Jirafa</t>
+          <t>GE03CUX03 Apertura</t>
         </is>
       </c>
       <c r="B650" s="5" t="n">
@@ -8907,7 +8907,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>Hisopado * Apertura WEB</t>
+          <t>CU10CUX02 La Jirafa</t>
         </is>
       </c>
       <c r="B651" s="5" t="n">
@@ -8920,7 +8920,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>MO06CUX02 Cómo usar Ecobici</t>
+          <t>DH11CUX05 Pedido de datos</t>
         </is>
       </c>
       <c r="B652" s="5" t="n">
@@ -8933,7 +8933,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>GE03CUX03 Apertura</t>
+          <t>ED03CUX05 Profesorados</t>
         </is>
       </c>
       <c r="B653" s="5" t="n">
@@ -8946,7 +8946,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>SUA01CUX22 Apertura desratización en colegios</t>
+          <t>DH11CUX07 Apertura</t>
         </is>
       </c>
       <c r="B654" s="5" t="n">
@@ -8959,20 +8959,20 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>DH02CUX01 Financiamiento</t>
+          <t>INN10CUX09 CA Ejecutar PI</t>
         </is>
       </c>
       <c r="B655" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C655" s="6" t="n">
-        <v>5.050946370566721e-06</v>
+        <v>4.545851733510049e-06</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>TU03CUX06 Apertura</t>
+          <t>GE03CUX02 TrabajoBA</t>
         </is>
       </c>
       <c r="B656" s="5" t="n">
@@ -8985,7 +8985,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>Realizar búsqueda de Código Postal por ubicación desde variable auxiliar</t>
+          <t>DEC05CUX02 Apertura</t>
         </is>
       </c>
       <c r="B657" s="5" t="n">
@@ -8998,7 +8998,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>Pedido de datos</t>
+          <t>TU03CUX06 Apertura</t>
         </is>
       </c>
       <c r="B658" s="5" t="n">
@@ -9011,7 +9011,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>Dónde lo hago | Identificación Tardía</t>
+          <t>​​DH02CUX01 Apertura corta​</t>
         </is>
       </c>
       <c r="B659" s="5" t="n">
@@ -9024,7 +9024,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>EDU05CUX02 * Apertura</t>
+          <t>NI02CUX01 Tiempo libre</t>
         </is>
       </c>
       <c r="B660" s="5" t="n">
@@ -9037,7 +9037,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>NI02CUX01 Tiempo libre</t>
+          <t>Derivación Becas Alimentarias - ⏳ Espero</t>
         </is>
       </c>
       <c r="B661" s="5" t="n">
@@ -9050,33 +9050,33 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>Encuesta</t>
+          <t>EDU05CUX02 * Apertura</t>
         </is>
       </c>
       <c r="B662" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C662" s="6" t="n">
-        <v>4.040757096453377e-06</v>
+        <v>4.545851733510049e-06</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>AMC04CUX04 Público general</t>
+          <t>Pedido de datos</t>
         </is>
       </c>
       <c r="B663" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C663" s="6" t="n">
-        <v>4.040757096453377e-06</v>
+        <v>4.545851733510049e-06</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>TR03CUX06 Servicios de salud para la prevención de zoonosis</t>
+          <t>Cómo es el trámite</t>
         </is>
       </c>
       <c r="B664" s="5" t="n">
@@ -9089,7 +9089,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>SE02CUX01 Cómo evitar estafas</t>
+          <t>DE03CUX02 Quiero hacer deporte</t>
         </is>
       </c>
       <c r="B665" s="5" t="n">
@@ -9102,7 +9102,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>DH08CUX03  Apertura de contingencia II</t>
+          <t>AI Otorgamiento</t>
         </is>
       </c>
       <c r="B666" s="5" t="n">
@@ -9115,7 +9115,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>CU11CUX02 Qué propuestas hay</t>
+          <t>Encuesta</t>
         </is>
       </c>
       <c r="B667" s="5" t="n">
@@ -9128,7 +9128,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>Cómo es el trámite</t>
+          <t>Realizar búsqueda de Código Postal por ubicación desde variable auxiliar</t>
         </is>
       </c>
       <c r="B668" s="5" t="n">
@@ -9141,7 +9141,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>DH01CUX04 Pregunta 2.1</t>
+          <t>CU01CUX14 Quiero ir</t>
         </is>
       </c>
       <c r="B669" s="5" t="n">
@@ -9154,7 +9154,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>AI Otorgamiento</t>
+          <t>SE02CUX01 Cómo evitar estafas</t>
         </is>
       </c>
       <c r="B670" s="5" t="n">
@@ -9167,7 +9167,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>DE03CUX02 Quiero hacer deporte</t>
+          <t>DH08CUX03  Apertura de contingencia II</t>
         </is>
       </c>
       <c r="B671" s="5" t="n">
@@ -9180,46 +9180,46 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>EDU03CUX09 Tengo una duda</t>
+          <t>EDU04CUX19 Apertura</t>
         </is>
       </c>
       <c r="B672" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C672" s="6" t="n">
-        <v>3.535662459396705e-06</v>
+        <v>4.040757096453377e-06</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>CU02CUX01 Teatro San Martín</t>
+          <t>AMC04CUX04 Público general</t>
         </is>
       </c>
       <c r="B673" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C673" s="6" t="n">
-        <v>3.535662459396705e-06</v>
+        <v>4.040757096453377e-06</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>Ver otra dirección de permitido estacionar</t>
+          <t>DH05CUX01 Hablar con alguien</t>
         </is>
       </c>
       <c r="B674" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C674" s="6" t="n">
-        <v>3.535662459396705e-06</v>
+        <v>4.040757096453377e-06</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>MO02CUX01 Lista de opciones</t>
+          <t>Dónde lo hago | Identificación Tardía</t>
         </is>
       </c>
       <c r="B675" s="5" t="n">
@@ -9232,7 +9232,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>TU03CUX14 Apertura</t>
+          <t>Test IABA Feedback by options</t>
         </is>
       </c>
       <c r="B676" s="5" t="n">
@@ -9245,7 +9245,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t xml:space="preserve">TR03CUX26 Apertura | Cajas Habilitadas </t>
+          <t>NI01CUX01 Superapertura Boticlásicos</t>
         </is>
       </c>
       <c r="B677" s="5" t="n">
@@ -9258,7 +9258,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>DH11CUX05 Pedido de datos</t>
+          <t>TU03CUX14 Apertura</t>
         </is>
       </c>
       <c r="B678" s="5" t="n">
@@ -9271,7 +9271,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>NI01CUX01 Superapertura Boticlásicos</t>
+          <t xml:space="preserve">TR03CUX26 Apertura | Cajas Habilitadas </t>
         </is>
       </c>
       <c r="B679" s="5" t="n">
@@ -9284,7 +9284,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>Pasaporte Covid | Revisar datos | Persistir info</t>
+          <t>VI01CUX01 Pagar tu crédito</t>
         </is>
       </c>
       <c r="B680" s="5" t="n">
@@ -9297,7 +9297,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>VI01CUX01 Pagar tu crédito</t>
+          <t>Ver otra dirección de permitido estacionar</t>
         </is>
       </c>
       <c r="B681" s="5" t="n">
@@ -9323,7 +9323,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>Dónde hacerlo | Certificado de Pobreza</t>
+          <t>Pasaporte Covid | Revisar datos | Persistir info</t>
         </is>
       </c>
       <c r="B683" s="5" t="n">
@@ -9336,7 +9336,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>​​DH02CUX01 Apertura corta​</t>
+          <t>Nada más</t>
         </is>
       </c>
       <c r="B684" s="5" t="n">
@@ -9349,7 +9349,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>DH11CUX07 Apertura</t>
+          <t>TR01CUX04 Cómo hago el trámite</t>
         </is>
       </c>
       <c r="B685" s="5" t="n">
@@ -9375,7 +9375,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>test ubicacion bax</t>
+          <t>TU02CUX01 Esquina Maradona</t>
         </is>
       </c>
       <c r="B687" s="5" t="n">
@@ -9388,7 +9388,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>Suaci - Error de foto obligatoria</t>
+          <t>Mostrar más Resultados | Servicio de Cercanía</t>
         </is>
       </c>
       <c r="B688" s="5" t="n">
@@ -9401,7 +9401,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>Mostrar más Resultados | Servicio de Cercanía</t>
+          <t>Hablar con operador</t>
         </is>
       </c>
       <c r="B689" s="5" t="n">
@@ -9414,7 +9414,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>SA01CUX01N Tips de prevención</t>
+          <t>Inactividad  del usuario: limpiar datos de sesión</t>
         </is>
       </c>
       <c r="B690" s="5" t="n">
@@ -9427,7 +9427,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>Hablar con operador</t>
+          <t>MO02CUX01 Apertura web</t>
         </is>
       </c>
       <c r="B691" s="5" t="n">
@@ -9440,7 +9440,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>MO10CUX01 Recorridos</t>
+          <t>test ubicacion bax</t>
         </is>
       </c>
       <c r="B692" s="5" t="n">
@@ -9453,7 +9453,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>TU02CUX01 Esquina Maradona</t>
+          <t>Dónde hacerlo | Certificado de Pobreza</t>
         </is>
       </c>
       <c r="B693" s="5" t="n">
@@ -9466,7 +9466,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>Nada más</t>
+          <t>SA08CUX02 Apertura</t>
         </is>
       </c>
       <c r="B694" s="5" t="n">
@@ -9479,7 +9479,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>Inactividad  del usuario: limpiar datos de sesión</t>
+          <t>SA01CUX01N Tips de prevención</t>
         </is>
       </c>
       <c r="B695" s="5" t="n">
@@ -9492,7 +9492,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>GE03CUX02 TrabajoBA</t>
+          <t>DH11CUX08 Introducción</t>
         </is>
       </c>
       <c r="B696" s="5" t="n">
@@ -9505,20 +9505,20 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>DH11CUX03 Apertura QR keywords</t>
+          <t xml:space="preserve">MO05CUX13 Apertura </t>
         </is>
       </c>
       <c r="B697" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C697" s="6" t="n">
-        <v>3.030567822340033e-06</v>
+        <v>2.525473185283361e-06</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>BX02CUX01 Pregunta 2</t>
+          <t>Lucho Test Segmento</t>
         </is>
       </c>
       <c r="B698" s="5" t="n">
@@ -9531,7 +9531,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>Cuánto cuesta | Fotocopia de Documentación Archivada</t>
+          <t>DH05CUX01 Apertura corta</t>
         </is>
       </c>
       <c r="B699" s="5" t="n">
@@ -9544,7 +9544,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>Qué necesito | Certificación de firmas</t>
+          <t>TR01CUX18 Pedí la constancia</t>
         </is>
       </c>
       <c r="B700" s="5" t="n">
@@ -9557,7 +9557,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>EDU04CUX19 Apertura</t>
+          <t>SE01CUX05 Apertura</t>
         </is>
       </c>
       <c r="B701" s="5" t="n">
@@ -9570,7 +9570,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>VI01CUX01 Hacer una consulta</t>
+          <t>Prueba DGCIUD</t>
         </is>
       </c>
       <c r="B702" s="5" t="n">
@@ -9583,7 +9583,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>CIU05CUX11 Cuestionario Flows</t>
+          <t xml:space="preserve">EDU04CUX30 Primera infancia </t>
         </is>
       </c>
       <c r="B703" s="5" t="n">
@@ -9596,7 +9596,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>DH11CUX08 Introducción</t>
+          <t>Qué necesito | Certificado de Pobreza</t>
         </is>
       </c>
       <c r="B704" s="5" t="n">
@@ -9609,7 +9609,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>Lucho Test Segmento</t>
+          <t>NI01CUX10 Inicio del cuento</t>
         </is>
       </c>
       <c r="B705" s="5" t="n">
@@ -9622,7 +9622,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t xml:space="preserve">MO05CUX13 Apertura </t>
+          <t>TU03CUX09 Qué hay para hacer</t>
         </is>
       </c>
       <c r="B706" s="5" t="n">
@@ -9635,7 +9635,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDU04CUX30 Primera infancia </t>
+          <t>CU10CUX02 Diógenes y el Linyera</t>
         </is>
       </c>
       <c r="B707" s="5" t="n">
@@ -9648,7 +9648,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>VI03CUX01  Quién puede pedirlo</t>
+          <t>Cuánto cuesta | Fotocopia de Documentación Archivada</t>
         </is>
       </c>
       <c r="B708" s="5" t="n">
@@ -9661,7 +9661,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>TR01CUX18 Pedí la constancia</t>
+          <t>MO06CUX03 Necesito ayuda</t>
         </is>
       </c>
       <c r="B709" s="5" t="n">
@@ -9674,7 +9674,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>DH05CUX01 Apertura corta</t>
+          <t>DDHH01CUX01 Residencia y DNI</t>
         </is>
       </c>
       <c r="B710" s="5" t="n">
@@ -9687,7 +9687,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>Prueba DGCIUD</t>
+          <t>VI03CUX01  Quién puede pedirlo</t>
         </is>
       </c>
       <c r="B711" s="5" t="n">
@@ -9700,72 +9700,72 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>CU10CUX02 Diógenes y el Linyera</t>
+          <t>Autos Abandonados - Intentar más tarde</t>
         </is>
       </c>
       <c r="B712" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C712" s="6" t="n">
-        <v>2.525473185283361e-06</v>
+        <v>2.020378548226688e-06</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>NI01CUX10 Inicio del cuento</t>
+          <t>DDHH03CUX02 Quiero adoptar</t>
         </is>
       </c>
       <c r="B713" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C713" s="6" t="n">
-        <v>2.525473185283361e-06</v>
+        <v>2.020378548226688e-06</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>TR01CUX10 Apertura &gt; Cómo hago el trámite</t>
+          <t>Levantamiento de clausura ascensor</t>
         </is>
       </c>
       <c r="B714" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C714" s="6" t="n">
-        <v>2.525473185283361e-06</v>
+        <v>2.020378548226688e-06</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>Qué necesito | Certificado de Pobreza</t>
+          <t>GA03CUX03 Dónde comer</t>
         </is>
       </c>
       <c r="B715" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C715" s="6" t="n">
-        <v>2.525473185283361e-06</v>
+        <v>2.020378548226688e-06</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>SE01CUX05 Apertura</t>
+          <t>DH02CUX01 Financiamiento</t>
         </is>
       </c>
       <c r="B716" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C716" s="6" t="n">
-        <v>2.525473185283361e-06</v>
+        <v>2.020378548226688e-06</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>SA08CUX02 Tengo una consulta</t>
+          <t>TR03CUX16 Denuncia a administradores de consorcio</t>
         </is>
       </c>
       <c r="B717" s="5" t="n">
@@ -9778,7 +9778,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>​​DH02CUX01 Requisitos​</t>
+          <t>EM04CUX01 Grabados</t>
         </is>
       </c>
       <c r="B718" s="5" t="n">
@@ -9791,7 +9791,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>CIU05CUX07 Quiero estudiar</t>
+          <t>TR03CUX09 Apertura</t>
         </is>
       </c>
       <c r="B719" s="5" t="n">
@@ -9804,7 +9804,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>CU01CUX10 Apertura</t>
+          <t>Mas info 2</t>
         </is>
       </c>
       <c r="B720" s="5" t="n">
@@ -9817,7 +9817,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>CU01CUX02 Palacio Noel</t>
+          <t xml:space="preserve">CU10CUX02 Esquina Mafalda &gt; Mapa </t>
         </is>
       </c>
       <c r="B721" s="5" t="n">
@@ -9830,7 +9830,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>TR04CUX16 Cómo lo tramito</t>
+          <t>Pasaporte Sanitario * Apertura &gt; Código QR</t>
         </is>
       </c>
       <c r="B722" s="5" t="n">
@@ -9843,7 +9843,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>DH11CUX07 Pedido de datos</t>
+          <t>Rendir subsidio 690</t>
         </is>
       </c>
       <c r="B723" s="5" t="n">
@@ -9856,7 +9856,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>DH11CUX05  Apertura estático principal</t>
+          <t>TUR01CUX03 Por lugar &gt; No sirve</t>
         </is>
       </c>
       <c r="B724" s="5" t="n">
@@ -9869,7 +9869,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>TR03CUX09 Apertura</t>
+          <t>Qué necesito | Certificación de firmas</t>
         </is>
       </c>
       <c r="B725" s="5" t="n">
@@ -9882,7 +9882,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>TR03CUX08 Obras</t>
+          <t xml:space="preserve">SE01CUX01 Cómo se cursa  </t>
         </is>
       </c>
       <c r="B726" s="5" t="n">
@@ -9895,7 +9895,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>TR03CUX08 Más de Habilitaciones</t>
+          <t>DH11CUX05 Encuesta</t>
         </is>
       </c>
       <c r="B727" s="5" t="n">
@@ -9908,7 +9908,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>Rendir subsidio 690</t>
+          <t>SUA01CUX011 Imagen - Error de formato, tamaño o peso - Extracción de árbol</t>
         </is>
       </c>
       <c r="B728" s="5" t="n">
@@ -9921,7 +9921,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t xml:space="preserve">CU10CUX02 Esquina Mafalda &gt; Mapa </t>
+          <t>ED03CUX05 Licenciaturas</t>
         </is>
       </c>
       <c r="B729" s="5" t="n">
@@ -9934,7 +9934,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t xml:space="preserve">SE01CUX01 Cómo se cursa  </t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="B730" s="5" t="n">
@@ -9947,7 +9947,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>Pasaporte Sanitario * Apertura &gt; Código QR</t>
+          <t>CU01CUX02 Palacio Noel</t>
         </is>
       </c>
       <c r="B731" s="5" t="n">
@@ -9960,163 +9960,163 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>TR03CUX16 Denuncia a administradores de consorcio</t>
+          <t>test enviar ubicación BAX</t>
         </is>
       </c>
       <c r="B732" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C732" s="6" t="n">
-        <v>2.020378548226688e-06</v>
+        <v>1.515283911170016e-06</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>DH01CUX04 Pregunta 2.2</t>
+          <t>DNI y OCR Scan</t>
         </is>
       </c>
       <c r="B733" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C733" s="6" t="n">
-        <v>2.020378548226688e-06</v>
+        <v>1.515283911170016e-06</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>SUA01CUX011 Imagen - Error de formato, tamaño o peso - Extracción de árbol</t>
+          <t>SA08CUX01 Buscar hospitales</t>
         </is>
       </c>
       <c r="B734" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C734" s="6" t="n">
-        <v>2.020378548226688e-06</v>
+        <v>1.515283911170016e-06</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>EM04CUX01 Grabados</t>
+          <t>CU01CUX11 Apertura</t>
         </is>
       </c>
       <c r="B735" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C735" s="6" t="n">
-        <v>2.020378548226688e-06</v>
+        <v>1.515283911170016e-06</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>SA08CUX02 Apertura</t>
+          <t>SUA01CUX27 pregunta refuerzos</t>
         </is>
       </c>
       <c r="B736" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C736" s="6" t="n">
-        <v>2.020378548226688e-06</v>
+        <v>1.515283911170016e-06</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>Mas info 2</t>
+          <t>CU01CUX08 Apertura</t>
         </is>
       </c>
       <c r="B737" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C737" s="6" t="n">
-        <v>2.020378548226688e-06</v>
+        <v>1.515283911170016e-06</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>DDHH01CUX01 Documentos</t>
+          <t>CU10CUX02 Isidoro Cañones</t>
         </is>
       </c>
       <c r="B738" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C738" s="6" t="n">
-        <v>2.020378548226688e-06</v>
+        <v>1.515283911170016e-06</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Respuestas generales a todos los canales</t>
         </is>
       </c>
       <c r="B739" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C739" s="6" t="n">
-        <v>2.020378548226688e-06</v>
+        <v>1.515283911170016e-06</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>Levantamiento de clausura ascensor</t>
+          <t>CIU05CUX08 Sitios históricos Belgrano</t>
         </is>
       </c>
       <c r="B740" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C740" s="6" t="n">
-        <v>2.020378548226688e-06</v>
+        <v>1.515283911170016e-06</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>SUA01CUX27 Dónde ubicar la luminaria</t>
+          <t>SA08CUX01 Requisitos</t>
         </is>
       </c>
       <c r="B741" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C741" s="6" t="n">
-        <v>2.020378548226688e-06</v>
+        <v>1.515283911170016e-06</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>SUA01CUX27 pregunta refuerzos</t>
+          <t>CU01CUX10 Apertura</t>
         </is>
       </c>
       <c r="B742" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C742" s="6" t="n">
-        <v>2.020378548226688e-06</v>
+        <v>1.515283911170016e-06</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>Autos Abandonados - Intentar más tarde</t>
+          <t>Validación Audios - Falla en el servicio</t>
         </is>
       </c>
       <c r="B743" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C743" s="6" t="n">
-        <v>2.020378548226688e-06</v>
+        <v>1.515283911170016e-06</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>Inactividad del usuario: Turismo MSFT</t>
+          <t>BX02CUX01 Pregunta 4</t>
         </is>
       </c>
       <c r="B744" s="5" t="n">
@@ -10129,7 +10129,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDU04CUX30 Apertura </t>
+          <t>BX02CUX01 Pregunta 2</t>
         </is>
       </c>
       <c r="B745" s="5" t="n">
@@ -10142,7 +10142,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>BX02CUX01 Pregunta 3</t>
+          <t>NI01CUX09 Siguen las huellas</t>
         </is>
       </c>
       <c r="B746" s="5" t="n">
@@ -10155,7 +10155,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>INN10CUX09 Preapertura</t>
+          <t>TR03CUX22 Alimentos en el espacio público</t>
         </is>
       </c>
       <c r="B747" s="5" t="n">
@@ -10168,7 +10168,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>TUR01CUX03 Seleccionar hora - Por Lugar</t>
+          <t>DDHH03CUX09 Qué necesito</t>
         </is>
       </c>
       <c r="B748" s="5" t="n">
@@ -10181,7 +10181,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>DE00CUX03 Polideportivos</t>
         </is>
       </c>
       <c r="B749" s="5" t="n">
@@ -10194,7 +10194,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>EDU04CUX30 Celu en el aula</t>
+          <t>GE03CUX02 Integración laboral</t>
         </is>
       </c>
       <c r="B750" s="5" t="n">
@@ -10207,7 +10207,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>SA08CUX01 Requisitos</t>
+          <t>DH02CUX01 Capacitaciones</t>
         </is>
       </c>
       <c r="B751" s="5" t="n">
@@ -10220,7 +10220,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>Dirección ya denunciada | Baches</t>
+          <t>DH11CUX05  Apertura estático principal</t>
         </is>
       </c>
       <c r="B752" s="5" t="n">
@@ -10233,7 +10233,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>DDHH03CUX04 Qué servicios hay</t>
+          <t>Cómo lo tramito | Identificación Tardía</t>
         </is>
       </c>
       <c r="B753" s="5" t="n">
@@ -10246,7 +10246,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>Respuestas generales a todos los canales</t>
+          <t>Audio</t>
         </is>
       </c>
       <c r="B754" s="5" t="n">
@@ -10272,7 +10272,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>TR01CUX03 Cómo hacer el trámite</t>
+          <t>Inactividad del usuario: Turismo MSFT</t>
         </is>
       </c>
       <c r="B756" s="5" t="n">
@@ -10285,7 +10285,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>CU02CUX02 Cómo sacar entradas</t>
+          <t>Copia Digital de Expediente o Documento  *Apertura &gt; Requisitos *Response</t>
         </is>
       </c>
       <c r="B757" s="5" t="n">
@@ -10298,7 +10298,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>MO06CUX03 Necesito ayuda</t>
+          <t>TR04CUX16 Cómo lo tramito</t>
         </is>
       </c>
       <c r="B758" s="5" t="n">
@@ -10311,7 +10311,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>GE03CUX02 Integración laboral</t>
+          <t>INN10CUX09 Preapertura</t>
         </is>
       </c>
       <c r="B759" s="5" t="n">
@@ -10324,7 +10324,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>TR02CUX04 Cómo es el trámite</t>
+          <t>Dirección ya denunciada | Baches</t>
         </is>
       </c>
       <c r="B760" s="5" t="n">
@@ -10337,189 +10337,189 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>CU10CUX02 Isidoro Cañones</t>
+          <t>EM04CUX02 Tipos de crédito mujeres emprendedoras</t>
         </is>
       </c>
       <c r="B761" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C761" s="6" t="n">
-        <v>1.515283911170016e-06</v>
+        <v>1.010189274113344e-06</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>ED03CUX05 Licenciaturas</t>
+          <t>Hablar con una persona derivado a WhatsApp</t>
         </is>
       </c>
       <c r="B762" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C762" s="6" t="n">
-        <v>1.515283911170016e-06</v>
+        <v>1.010189274113344e-06</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>EM04CUX02 Ver requisitos mujeres emprendedoras</t>
+          <t>CUL02CUX03 Iglesias y templos Caballito</t>
         </is>
       </c>
       <c r="B763" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C763" s="6" t="n">
-        <v>1.515283911170016e-06</v>
+        <v>1.010189274113344e-06</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>CU01CUX08 Apertura</t>
+          <t xml:space="preserve">SE01CUX01 Proceso de Selección </t>
         </is>
       </c>
       <c r="B764" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C764" s="6" t="n">
-        <v>1.515283911170016e-06</v>
+        <v>1.010189274113344e-06</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>CU01CUX11 Apertura</t>
+          <t>CIU05CUX11 Validación de barrio</t>
         </is>
       </c>
       <c r="B765" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C765" s="6" t="n">
-        <v>1.515283911170016e-06</v>
+        <v>1.010189274113344e-06</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>GA03CUX03 Dónde comer</t>
+          <t>CIU05CUX11 Envío exitoso</t>
         </is>
       </c>
       <c r="B766" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C766" s="6" t="n">
-        <v>1.515283911170016e-06</v>
+        <v>1.010189274113344e-06</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Sitios históricos Belgrano</t>
+          <t>TR01CUX10 Qué necesito</t>
         </is>
       </c>
       <c r="B767" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C767" s="6" t="n">
-        <v>1.515283911170016e-06</v>
+        <v>1.010189274113344e-06</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>test enviar ubicación BAX</t>
+          <t>NI01CUX11 Apertura inicio</t>
         </is>
       </c>
       <c r="B768" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C768" s="6" t="n">
-        <v>1.515283911170016e-06</v>
+        <v>1.010189274113344e-06</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>DH11CUX05 Encuesta</t>
+          <t>NI01CUX11 Sí (Primer acto)</t>
         </is>
       </c>
       <c r="B769" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C769" s="6" t="n">
-        <v>1.515283911170016e-06</v>
+        <v>1.010189274113344e-06</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>DH11CUX05 Mensaje final</t>
+          <t>TR02CUX04 Qué necesito</t>
         </is>
       </c>
       <c r="B770" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C770" s="6" t="n">
-        <v>1.515283911170016e-06</v>
+        <v>1.010189274113344e-06</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>DNI y OCR Scan</t>
+          <t>SA08CUX02 Tengo una consulta</t>
         </is>
       </c>
       <c r="B771" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C771" s="6" t="n">
-        <v>1.515283911170016e-06</v>
+        <v>1.010189274113344e-06</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>EP04CUX01 Chat por WhatsApp</t>
+          <t>SUA01CUX15 Dirección</t>
         </is>
       </c>
       <c r="B772" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C772" s="6" t="n">
-        <v>1.515283911170016e-06</v>
+        <v>1.010189274113344e-06</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>TUR01CUX03 Elegir tipo de turrno</t>
+          <t>SUA01CUX33 Apertura</t>
         </is>
       </c>
       <c r="B773" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C773" s="6" t="n">
-        <v>1.515283911170016e-06</v>
+        <v>1.010189274113344e-06</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>Validación Audios - Falla en el servicio</t>
+          <t>​​DH02CUX01 Requisitos​</t>
         </is>
       </c>
       <c r="B774" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C774" s="6" t="n">
-        <v>1.515283911170016e-06</v>
+        <v>1.010189274113344e-06</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>CUL02CUX01 Apertura</t>
+          <t>​​DH02CUX01 Beneficios impositivos​</t>
         </is>
       </c>
       <c r="B775" s="5" t="n">
@@ -10532,7 +10532,7 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>NI01CUX11 Sí (Primer acto)</t>
+          <t>EM03CUX02 Cursos presenciales</t>
         </is>
       </c>
       <c r="B776" s="5" t="n">
@@ -10545,7 +10545,7 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>NI01CUX07 Principio</t>
+          <t>DH02CUX01 Quiero anotarme</t>
         </is>
       </c>
       <c r="B777" s="5" t="n">
@@ -10558,7 +10558,7 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>Mostrar más Resultados | Ecobici</t>
+          <t>TU03CUX08 Apertura</t>
         </is>
       </c>
       <c r="B778" s="5" t="n">
@@ -10571,7 +10571,7 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>SE01CUX01 Quiero inscribirme</t>
+          <t>DE00CUX03 Escuelas deportivas</t>
         </is>
       </c>
       <c r="B779" s="5" t="n">
@@ -10584,7 +10584,7 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>CUL02CUX03 Iglesias y templos Caballito</t>
+          <t>TR03CUX08 Obras</t>
         </is>
       </c>
       <c r="B780" s="5" t="n">
@@ -10597,7 +10597,7 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>Código postal - No pudo encontrarlo por ubicación</t>
+          <t>MO10CUX01 Otros recorridos</t>
         </is>
       </c>
       <c r="B781" s="5" t="n">
@@ -10610,7 +10610,7 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>Cómo hacerlo | Certificación de firmas</t>
+          <t>MO10CUX01 Recorridos</t>
         </is>
       </c>
       <c r="B782" s="5" t="n">
@@ -10636,7 +10636,7 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>Filtro de segurización</t>
+          <t>TR03CUX08 Habilitación vehicular de foodtrucks</t>
         </is>
       </c>
       <c r="B784" s="5" t="n">
@@ -10649,7 +10649,7 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>TR01CUX04 Requisitos</t>
+          <t>TR05CUX04 CUIT CUIL inválido</t>
         </is>
       </c>
       <c r="B785" s="5" t="n">
@@ -10662,7 +10662,7 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>TR01CUX04 Cómo hago el trámite</t>
+          <t>Centralizar rúbrica</t>
         </is>
       </c>
       <c r="B786" s="5" t="n">
@@ -10675,7 +10675,7 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>DDHH03CUX02 Talleres</t>
+          <t>TR03CUX25 Cómo pagar boletas</t>
         </is>
       </c>
       <c r="B787" s="5" t="n">
@@ -10688,7 +10688,7 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>MO10CUX04 Apertura</t>
+          <t>TR03CUX08 Más de Habilitaciones</t>
         </is>
       </c>
       <c r="B788" s="5" t="n">
@@ -10701,7 +10701,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>SUA01CUX33 Apertura</t>
+          <t>DDHH03CUX04 Qué servicios hay</t>
         </is>
       </c>
       <c r="B789" s="5" t="n">
@@ -10714,7 +10714,7 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>SA08CUX01 Buscar hospitales</t>
+          <t>BX02CUX01 Pregunta 3</t>
         </is>
       </c>
       <c r="B790" s="5" t="n">
@@ -10727,7 +10727,7 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>Bicicletas (Apertura) &gt; Dónde dejar la bici * Ap de flow</t>
+          <t>Código postal - No pudo encontrarlo por ubicación</t>
         </is>
       </c>
       <c r="B791" s="5" t="n">
@@ -10740,7 +10740,7 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>TUR01CUX03 Validación turno</t>
+          <t>Insultos</t>
         </is>
       </c>
       <c r="B792" s="5" t="n">
@@ -10753,7 +10753,7 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>OB05CUX01 Tramitación registro Plano obra civil - 3C</t>
+          <t xml:space="preserve">TRO4CUX32  Subintent errores </t>
         </is>
       </c>
       <c r="B793" s="5" t="n">
@@ -10766,7 +10766,7 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>Insultos</t>
+          <t>JU03CUX01 Qué necesito</t>
         </is>
       </c>
       <c r="B794" s="5" t="n">
@@ -10779,7 +10779,7 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>Derivación Becas Alimentarias - ⏳ Espero</t>
+          <t>GA03CUX03 Apertura corta</t>
         </is>
       </c>
       <c r="B795" s="5" t="n">
@@ -10792,7 +10792,7 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>CU01CUX15 - Encontramos a Kindl</t>
+          <t>TUR01CUX03 Elegir fecha</t>
         </is>
       </c>
       <c r="B796" s="5" t="n">
@@ -10805,7 +10805,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>TR05CUX04 CUIT CUIL inválido</t>
+          <t xml:space="preserve">EDU04CUX30 Apertura </t>
         </is>
       </c>
       <c r="B797" s="5" t="n">
@@ -10818,7 +10818,7 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>TU03CUX08 Apertura</t>
+          <t>DH03CUX03 Buscar APND</t>
         </is>
       </c>
       <c r="B798" s="5" t="n">
@@ -10831,7 +10831,7 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>DH11CUX05 Responder pregunta V1</t>
+          <t>DH07CUX01 Acompañamiento</t>
         </is>
       </c>
       <c r="B799" s="5" t="n">
@@ -10844,7 +10844,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>​​DH02CUX01 Beneficios impositivos​</t>
+          <t>TUR01CUX03 Por lugar &gt; No sirve &gt; dirección verificada</t>
         </is>
       </c>
       <c r="B800" s="5" t="n">
@@ -10857,7 +10857,7 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>DH11CUX07 Validación de datos</t>
+          <t>TUR01CUX03 Seleccionar hora - Por Lugar</t>
         </is>
       </c>
       <c r="B801" s="5" t="n">
@@ -10870,7 +10870,7 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>DH11CUX08 Pedido de datos</t>
+          <t>DH11CUX07 Introducción</t>
         </is>
       </c>
       <c r="B802" s="5" t="n">
@@ -10883,7 +10883,7 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>TU03CUX02 Apertura</t>
+          <t>DH11CUX05 Responde bien V1</t>
         </is>
       </c>
       <c r="B803" s="5" t="n">
@@ -10896,7 +10896,7 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRO4CUX32  Subintent errores </t>
+          <t>DH11CUX03 Repaso MTV4</t>
         </is>
       </c>
       <c r="B804" s="5" t="n">
@@ -10909,7 +10909,7 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>Centralizar rúbrica</t>
+          <t>DH11CUX03  Apertura estático principal</t>
         </is>
       </c>
       <c r="B805" s="5" t="n">
@@ -10922,7 +10922,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>EM03CUX02 Cursos presenciales</t>
+          <t xml:space="preserve">DH07CUX01 Cómo anotarme </t>
         </is>
       </c>
       <c r="B806" s="5" t="n">
@@ -10935,7 +10935,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>MO06CUX01 Dónde dejar la bici</t>
+          <t>TU03CUX02 Apertura</t>
         </is>
       </c>
       <c r="B807" s="5" t="n">
@@ -10948,7 +10948,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>SIGEHOS &gt; Usuario no responde pregunta</t>
+          <t>TR01CUX10 Apertura &gt; Cómo hago el trámite</t>
         </is>
       </c>
       <c r="B808" s="5" t="n">
@@ -10961,7 +10961,7 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>MO02CUX01 Apertura web</t>
+          <t>SIGEHOS &gt; Usuario no responde pregunta</t>
         </is>
       </c>
       <c r="B809" s="5" t="n">
@@ -10974,7 +10974,7 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>TUR01CUX03 Por fecha</t>
+          <t>VI01CUX07 Monto del préstamo</t>
         </is>
       </c>
       <c r="B810" s="5" t="n">
@@ -10987,7 +10987,7 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>​​DH02CUX01 FONDES​</t>
+          <t>TR01CUX09 Cómo hago el trámite</t>
         </is>
       </c>
       <c r="B811" s="5" t="n">
@@ -11000,7 +11000,7 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>SUA01CUX20 Pedido de barrio</t>
+          <t>Bicicletas (Apertura) &gt; Dónde dejar la bici * Ap de flow</t>
         </is>
       </c>
       <c r="B812" s="5" t="n">
@@ -11013,7 +11013,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>DH03CUX03 Acompañantes</t>
+          <t>TU01CUX02 NO</t>
         </is>
       </c>
       <c r="B813" s="5" t="n">
@@ -11026,7 +11026,7 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>NI01CUX11 Apertura inicio</t>
+          <t>CUL02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B814" s="5" t="n">
@@ -11039,7 +11039,7 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>Hablar con una persona derivado a WhatsApp</t>
+          <t>DEC05CUX02 De qué se trata</t>
         </is>
       </c>
       <c r="B815" s="5" t="n">
@@ -11052,7 +11052,7 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>TR01CUX10 Qué necesito</t>
+          <t>Filtro de segurización</t>
         </is>
       </c>
       <c r="B816" s="5" t="n">
@@ -11065,7 +11065,7 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>DH11CUX03 MTV4</t>
+          <t>TU03CUX09 Shows en el domo</t>
         </is>
       </c>
       <c r="B817" s="5" t="n">
@@ -11078,7 +11078,7 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>DH11CUX08 Video 1</t>
+          <t>DEC05CUX02 Cómo participo</t>
         </is>
       </c>
       <c r="B818" s="5" t="n">
@@ -11091,59 +11091,59 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>DH11CUX03  Apertura estático principal</t>
+          <t>NI01CUX10 Ahora no</t>
         </is>
       </c>
       <c r="B819" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C819" s="6" t="n">
-        <v>1.010189274113344e-06</v>
+        <v>5.050946370566721e-07</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>SUA01CUX15 Dirección</t>
+          <t>NI01CUX11 Tunel en grupo plot point II</t>
         </is>
       </c>
       <c r="B820" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C820" s="6" t="n">
-        <v>1.010189274113344e-06</v>
+        <v>5.050946370566721e-07</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>TR03CUX03 Proteatro</t>
+          <t>NI01CUX11 Sí (Plot point 1)</t>
         </is>
       </c>
       <c r="B821" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C821" s="6" t="n">
-        <v>1.010189274113344e-06</v>
+        <v>5.050946370566721e-07</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>DH02CUX01 Quiero anotarme</t>
+          <t>TR02CUX04 Cómo es el trámite</t>
         </is>
       </c>
       <c r="B822" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C822" s="6" t="n">
-        <v>1.010189274113344e-06</v>
+        <v>5.050946370566721e-07</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>¿En qué consiste el trámite de Modificación de Datos?</t>
+          <t>CIU05CUX08 Sitios Históricos Devoto</t>
         </is>
       </c>
       <c r="B823" s="5" t="n">
@@ -11156,7 +11156,7 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>test link</t>
+          <t>CIU05CUX12 Envío exitoso</t>
         </is>
       </c>
       <c r="B824" s="5" t="n">
@@ -11169,7 +11169,7 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>test.muestra.filacero</t>
+          <t>CIU05CUX10 Murales La Boca</t>
         </is>
       </c>
       <c r="B825" s="5" t="n">
@@ -11182,7 +11182,7 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>INN10CUX11 Pregunta tono</t>
+          <t>TR01CUX15 Requisitos</t>
         </is>
       </c>
       <c r="B826" s="5" t="n">
@@ -11195,7 +11195,7 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>Ignorar</t>
+          <t>SA08CUX02 Recibí un trasplante / En lista de espera</t>
         </is>
       </c>
       <c r="B827" s="5" t="n">
@@ -11208,7 +11208,7 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>NI01CUX07 Galera</t>
+          <t>CU02CUX02 Info útil</t>
         </is>
       </c>
       <c r="B828" s="5" t="n">
@@ -11221,7 +11221,7 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>NI01CUX06 Con muchas aceitunas</t>
+          <t>CIU05CUX08 Silos de Dorrego</t>
         </is>
       </c>
       <c r="B829" s="5" t="n">
@@ -11234,7 +11234,7 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>Código postal - No pudo encontrarlo por domicilio</t>
+          <t>CIU05CUX10 Murales Colegiales</t>
         </is>
       </c>
       <c r="B830" s="5" t="n">
@@ -11247,7 +11247,7 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>NI01CUX03  El de Pintor</t>
+          <t>CIU05CUX10 Murales Devoto</t>
         </is>
       </c>
       <c r="B831" s="5" t="n">
@@ -11260,7 +11260,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>TR01CUX01 Requisitos</t>
+          <t>Qué necesito espectáculos musicales en vivo</t>
         </is>
       </c>
       <c r="B832" s="5" t="n">
@@ -11273,7 +11273,7 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>Derivación desde la web</t>
+          <t>PC03CUX01 Voluntarios BA</t>
         </is>
       </c>
       <c r="B833" s="5" t="n">
@@ -11286,7 +11286,7 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>SA08CUX02 Recibí un trasplante / En lista de espera</t>
+          <t>CU09CUX03 Curiosidatos</t>
         </is>
       </c>
       <c r="B834" s="5" t="n">
@@ -11299,7 +11299,7 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>Suscribir | Clima</t>
+          <t>CU10CUX01 Casco Histórico</t>
         </is>
       </c>
       <c r="B835" s="5" t="n">
@@ -11312,7 +11312,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>Disambiguation Intent</t>
+          <t>CU11CUX03 Chacarita (Carlos Gardel)</t>
         </is>
       </c>
       <c r="B836" s="5" t="n">
@@ -11325,7 +11325,7 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>JU03CUX01 Tengo una consulta</t>
+          <t>SA16CUX02 Cómo se transmite</t>
         </is>
       </c>
       <c r="B837" s="5" t="n">
@@ -11338,7 +11338,7 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>DDHH03CUX02 Quiero adoptar</t>
+          <t>CIU05CUX10 Avatares de Caballito</t>
         </is>
       </c>
       <c r="B838" s="5" t="n">
@@ -11351,7 +11351,7 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>JU03CUX01 Qué necesito</t>
+          <t>TR01CUX03 Cómo hacer el trámite</t>
         </is>
       </c>
       <c r="B839" s="5" t="n">
@@ -11364,7 +11364,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>BX02CUX01 Pregunta 4</t>
+          <t>TR01CUX09 Qué necesito</t>
         </is>
       </c>
       <c r="B840" s="5" t="n">
@@ -11377,7 +11377,7 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>OB05CUX01 Subsanación - 4D</t>
+          <t>CIU05CUX08 Parque Onega</t>
         </is>
       </c>
       <c r="B841" s="5" t="n">
@@ -11390,7 +11390,7 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>Opción 1</t>
+          <t>CU02CUX01 Teatro Cervantes</t>
         </is>
       </c>
       <c r="B842" s="5" t="n">
@@ -11403,7 +11403,7 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>JU02CUX01 Hacer una consulta</t>
+          <t>CU02CUX02 Cómo sacar entradas</t>
         </is>
       </c>
       <c r="B843" s="5" t="n">
@@ -11416,7 +11416,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>CU09CUX03 Dónde queda</t>
+          <t>SUA01CUX20 Cuestionario - Alcance</t>
         </is>
       </c>
       <c r="B844" s="5" t="n">
@@ -11429,7 +11429,7 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>Feedback a humano - Unificado - No resolvió</t>
+          <t>CO12CUX02 Número de emergencia</t>
         </is>
       </c>
       <c r="B845" s="5" t="n">
@@ -11442,7 +11442,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>MO09CUX04 Cortes y desvíos</t>
+          <t>SUA01CUX20 Pregunta pasillo</t>
         </is>
       </c>
       <c r="B846" s="5" t="n">
@@ -11455,7 +11455,7 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>CU09CUX03 Curiosidatos</t>
+          <t>CU01CUX09 Apertura</t>
         </is>
       </c>
       <c r="B847" s="5" t="n">
@@ -11468,7 +11468,7 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>CU09CUX03 Visitas guiadas</t>
+          <t>Suscribir | Clima</t>
         </is>
       </c>
       <c r="B848" s="5" t="n">
@@ -11481,7 +11481,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>TR01CUX15 Hacer el registro</t>
+          <t>SUA01CUX26 Pedido de número de expediente</t>
         </is>
       </c>
       <c r="B849" s="5" t="n">
@@ -11494,7 +11494,7 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>CU10CUX01 Visitas guiadas</t>
+          <t>CU01CUX08 BA: Punto de Partida</t>
         </is>
       </c>
       <c r="B850" s="5" t="n">
@@ -11507,7 +11507,7 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>EDU05CUX02 * Estudio en BA</t>
+          <t>fulfilled of Happy Path</t>
         </is>
       </c>
       <c r="B851" s="5" t="n">
@@ -11520,7 +11520,7 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>DE02CUX01 Cómo funcionan</t>
+          <t>¿En qué consiste el trámite de Modificación de Datos?</t>
         </is>
       </c>
       <c r="B852" s="5" t="n">
@@ -11533,7 +11533,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>DE00CUX03 Polideportivos</t>
+          <t>test.muestra.filacero</t>
         </is>
       </c>
       <c r="B853" s="5" t="n">
@@ -11546,7 +11546,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>EDU05CUX02 * Study BA</t>
+          <t>DH11CUX08 Validación de datos</t>
         </is>
       </c>
       <c r="B854" s="5" t="n">
@@ -11559,7 +11559,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>EM04CUX01 En vivo</t>
+          <t>DH11CUX08 Silencio user video 1</t>
         </is>
       </c>
       <c r="B855" s="5" t="n">
@@ -11572,7 +11572,7 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>DDHH03CUX01 Chicos perdidos</t>
+          <t>Dale/OK</t>
         </is>
       </c>
       <c r="B856" s="5" t="n">
@@ -11585,7 +11585,7 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>DDHH03CUX02 Espera activa</t>
+          <t>VI01CUX06 Monto del préstamo</t>
         </is>
       </c>
       <c r="B857" s="5" t="n">
@@ -11598,7 +11598,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>TR01CUX09 Qué necesito</t>
+          <t>VI01CUX06 Sobre el programa</t>
         </is>
       </c>
       <c r="B858" s="5" t="n">
@@ -11611,7 +11611,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>Carrousel</t>
+          <t xml:space="preserve">VI03CUX01 Cómo funciona </t>
         </is>
       </c>
       <c r="B859" s="5" t="n">
@@ -11624,7 +11624,7 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>OB05CUX01 Otro estado - 6A</t>
+          <t>fulfilled of SALUD</t>
         </is>
       </c>
       <c r="B860" s="5" t="n">
@@ -11637,7 +11637,7 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>Nuevo ambiente Uli fechas</t>
+          <t>test link</t>
         </is>
       </c>
       <c r="B861" s="5" t="n">
@@ -11650,7 +11650,7 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>NI01CUX11 Tunel en grupo plot point II</t>
+          <t>fulfilled of OPERADOR</t>
         </is>
       </c>
       <c r="B862" s="5" t="n">
@@ -11663,7 +11663,7 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>DH11CUX05 Responde mal V4</t>
+          <t>fulfilled of ADICCIONES</t>
         </is>
       </c>
       <c r="B863" s="5" t="n">
@@ -11676,7 +11676,7 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>DH11CUX05  Apertura de contingencia I</t>
+          <t>​​DH02CUX01 FONDES​</t>
         </is>
       </c>
       <c r="B864" s="5" t="n">
@@ -11689,7 +11689,7 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>NI01CUX11 Sí (Plot point 1)</t>
+          <t>CU01CUX15 Comienzo - Cabras Pista 1</t>
         </is>
       </c>
       <c r="B865" s="5" t="n">
@@ -11702,7 +11702,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>Derivacion especialista</t>
+          <t>CU01CUX11 BA en construcción</t>
         </is>
       </c>
       <c r="B866" s="5" t="n">
@@ -11715,7 +11715,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>Dale/OK</t>
+          <t>CU01CUX10 BA Punto de partida</t>
         </is>
       </c>
       <c r="B867" s="5" t="n">
@@ -11728,7 +11728,7 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>NI01CUX09 Subir a la calesita</t>
+          <t>TR01CUX01 Requisitos</t>
         </is>
       </c>
       <c r="B868" s="5" t="n">
@@ -11741,7 +11741,7 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>NI01CUX09 Siguen las huellas</t>
+          <t xml:space="preserve">CU01CUX15 Mr. M </t>
         </is>
       </c>
       <c r="B869" s="5" t="n">
@@ -11754,7 +11754,7 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>NI01CUX09 Pista de skate</t>
+          <t>CU01CUX15 Las Cabras Macabras</t>
         </is>
       </c>
       <c r="B870" s="5" t="n">
@@ -11767,7 +11767,7 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t xml:space="preserve">NI01CUX09 Asientos </t>
+          <t>CIU05CUX08 Palacio Hirsch</t>
         </is>
       </c>
       <c r="B871" s="5" t="n">
@@ -11780,7 +11780,7 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>NI01CUX09 Sí, dale (Primer acto)</t>
+          <t>Carrousel</t>
         </is>
       </c>
       <c r="B872" s="5" t="n">
@@ -11793,7 +11793,7 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>NI01CUX10 Ahora no</t>
+          <t>Mostrar más Resultados | Ecobici</t>
         </is>
       </c>
       <c r="B873" s="5" t="n">
@@ -11806,7 +11806,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>Qué necesito espectáculos musicales en vivo</t>
+          <t>Nuevo ambiente Uli fechas</t>
         </is>
       </c>
       <c r="B874" s="5" t="n">
@@ -11819,7 +11819,7 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>CU02CUX02 Programación</t>
+          <t>TR03CUX07 Apertura Inscripción al registro público de salvavidas</t>
         </is>
       </c>
       <c r="B875" s="5" t="n">
@@ -11832,7 +11832,7 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>NI01CUX09 Ahora no</t>
+          <t>Ignorar</t>
         </is>
       </c>
       <c r="B876" s="5" t="n">
@@ -11845,7 +11845,7 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>NI01CUX08 Principio</t>
+          <t>INN10CUX11 Pregunta tono</t>
         </is>
       </c>
       <c r="B877" s="5" t="n">
@@ -11858,7 +11858,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>SUA01CUX20 Pregunta pasillo</t>
+          <t>INN07CUX02 Tecweek Play</t>
         </is>
       </c>
       <c r="B878" s="5" t="n">
@@ -11871,7 +11871,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t xml:space="preserve">CU01CUX15 Mr. M </t>
+          <t>INN09CUX01 Qué necesito</t>
         </is>
       </c>
       <c r="B879" s="5" t="n">
@@ -11884,7 +11884,7 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>INN07CUX02 Tecweek Play</t>
+          <t>INN07CUX02 Apertura corta</t>
         </is>
       </c>
       <c r="B880" s="5" t="n">
@@ -11897,7 +11897,7 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>TU01CUX02 NO</t>
+          <t>DDHH03CUX01 Chicos perdidos</t>
         </is>
       </c>
       <c r="B881" s="5" t="n">
@@ -11910,7 +11910,7 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>CU01CUX15 Atlas</t>
+          <t>DDHH03CUX02 Espera activa</t>
         </is>
       </c>
       <c r="B882" s="5" t="n">
@@ -11923,7 +11923,7 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>GA03CUX03 Apertura corta</t>
+          <t>Código postal - No pudo encontrarlo por domicilio</t>
         </is>
       </c>
       <c r="B883" s="5" t="n">
@@ -11936,7 +11936,7 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>CO08CUX07 Sobre las pistas</t>
+          <t>JU03CUX01 Tengo una consulta</t>
         </is>
       </c>
       <c r="B884" s="5" t="n">
@@ -11949,7 +11949,7 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>CU01CUX11 BA en construcción</t>
+          <t>JU02CUX01 Hacer una consulta</t>
         </is>
       </c>
       <c r="B885" s="5" t="n">
@@ -11975,7 +11975,7 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>INN07CUX02 Apertura corta</t>
+          <t>MO09CUX04 Cortes y desvíos</t>
         </is>
       </c>
       <c r="B887" s="5" t="n">
@@ -11988,7 +11988,7 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>CU01CUX08 BA: Punto de Partida</t>
+          <t>DDHH01CUX01 Documentos</t>
         </is>
       </c>
       <c r="B888" s="5" t="n">
@@ -12001,7 +12001,7 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>TR03CUX26 Cómo hago el trámite</t>
+          <t>DDHH03CUX04 Dónde quedan</t>
         </is>
       </c>
       <c r="B889" s="5" t="n">
@@ -12014,7 +12014,7 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>CU01CUX09 Patio</t>
+          <t>OB05CUX01 Número de expediente erróneo</t>
         </is>
       </c>
       <c r="B890" s="5" t="n">
@@ -12027,7 +12027,7 @@
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>TR03CUX22 Alimentos en el espacio público</t>
+          <t>Opción 1</t>
         </is>
       </c>
       <c r="B891" s="5" t="n">
@@ -12040,7 +12040,7 @@
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>CIU05CUX12 Envío exitoso</t>
+          <t>NI01CUX09 Ahora no</t>
         </is>
       </c>
       <c r="B892" s="5" t="n">
@@ -12053,7 +12053,7 @@
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>CIU05CUX11 Validación de barrio</t>
+          <t>NI01CUX08 Principio</t>
         </is>
       </c>
       <c r="B893" s="5" t="n">
@@ -12066,7 +12066,7 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>CIU05CUX11 Envío exitoso</t>
+          <t>NI01CUX07 Un silbato</t>
         </is>
       </c>
       <c r="B894" s="5" t="n">
@@ -12079,7 +12079,7 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>CIU05CUX10 Murales La Boca</t>
+          <t>NI01CUX07 Principio</t>
         </is>
       </c>
       <c r="B895" s="5" t="n">
@@ -12092,7 +12092,7 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>CIU05CUX10 Murales Devoto</t>
+          <t>NI01CUX07 Galera</t>
         </is>
       </c>
       <c r="B896" s="5" t="n">
@@ -12105,7 +12105,7 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>CIU05CUX10 Avatares de Caballito</t>
+          <t>NI01CUX06 Línea D</t>
         </is>
       </c>
       <c r="B897" s="5" t="n">
@@ -12118,7 +12118,7 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>CIU05CUX10 Alicia y el conejo</t>
+          <t>NI01CUX03  El de Pintor</t>
         </is>
       </c>
       <c r="B898" s="5" t="n">
@@ -12131,7 +12131,7 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>TU03CUX09 Shows en el domo</t>
+          <t xml:space="preserve">NI01CUX09 Asientos </t>
         </is>
       </c>
       <c r="B899" s="5" t="n">
@@ -12144,7 +12144,7 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>CO12CUX02 Número de emergencia</t>
+          <t>MO10CUX06 Líneas</t>
         </is>
       </c>
       <c r="B900" s="5" t="n">
@@ -12157,7 +12157,7 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>TU03CUX09 Museo</t>
+          <t>MO10CUX04 Líneas</t>
         </is>
       </c>
       <c r="B901" s="5" t="n">
@@ -12170,7 +12170,7 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>DH11CUX05 Responder pregunta V3</t>
+          <t>MO10CUX04 Apertura</t>
         </is>
       </c>
       <c r="B902" s="5" t="n">
@@ -12183,7 +12183,7 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>TUR01CUX13 Ya tenía turno</t>
+          <t>NI01CUX09 Sí, dale (Primer acto)</t>
         </is>
       </c>
       <c r="B903" s="5" t="n">
@@ -12196,7 +12196,7 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>Ubicación no encontrada | Ecobici</t>
+          <t>TR03CUX25 Estado de mi trámite</t>
         </is>
       </c>
       <c r="B904" s="5" t="n">
@@ -12209,7 +12209,7 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>AM04CUX02 Qué hay para hacer</t>
+          <t>TU03CUX09 Museo</t>
         </is>
       </c>
       <c r="B905" s="5" t="n">
@@ -12222,7 +12222,7 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>Test.apertura.filaCero</t>
+          <t>Feedback a humano - Unificado - No resolvió por Audiencia</t>
         </is>
       </c>
       <c r="B906" s="5" t="n">
@@ -12235,7 +12235,7 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>Tagear IA Off</t>
+          <t>GE01CUX03 Cómo puedo ayudar</t>
         </is>
       </c>
       <c r="B907" s="5" t="n">
@@ -12248,7 +12248,7 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Sitios Históricos La Boca</t>
+          <t>AM04CUX05 Qué hay para hacer</t>
         </is>
       </c>
       <c r="B908" s="5" t="n">
@@ -12261,7 +12261,7 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Sitios Históricos Devoto</t>
+          <t>AM04CUX04 Visitas guiadas</t>
         </is>
       </c>
       <c r="B909" s="5" t="n">
@@ -12274,7 +12274,7 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Silos de Dorrego</t>
+          <t>AM04CUX03 Cómo se recuperó</t>
         </is>
       </c>
       <c r="B910" s="5" t="n">
@@ -12287,7 +12287,7 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Estatua de la Libertad</t>
+          <t>AM04CUX02 Qué hay para hacer</t>
         </is>
       </c>
       <c r="B911" s="5" t="n">
@@ -12300,7 +12300,7 @@
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>DH11CUX08 Repaso video 1</t>
+          <t>TUR01CUX03 Por fecha</t>
         </is>
       </c>
       <c r="B912" s="5" t="n">
@@ -12313,7 +12313,7 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>DH11CUX07 Repaso V1</t>
+          <t>EM04CUX01 En vivo</t>
         </is>
       </c>
       <c r="B913" s="5" t="n">
@@ -12326,7 +12326,7 @@
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>AM04CUX05 El vivero</t>
+          <t>EP04CUX01 Chat por WhatsApp</t>
         </is>
       </c>
       <c r="B914" s="5" t="n">
@@ -12339,7 +12339,7 @@
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>TUR01CUX03 Por lugar &gt; No sirve &gt; dirección verificada</t>
+          <t xml:space="preserve">DH02CUX01 Oportunidades </t>
         </is>
       </c>
       <c r="B915" s="5" t="n">
@@ -12352,7 +12352,7 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>VI01CUX06 Sobre el programa</t>
+          <t>EM04CUX02 Ver requisitos mujeres emprendedoras</t>
         </is>
       </c>
       <c r="B916" s="5" t="n">
@@ -12365,7 +12365,7 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>VI01CUX06 Monto del préstamo</t>
+          <t>DE02CUX01 Colonia accesible</t>
         </is>
       </c>
       <c r="B917" s="5" t="n">
@@ -12378,7 +12378,7 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>fulfilled of SUBSIDIO</t>
+          <t>EDU05CUX02 * Qué puedo estudiar</t>
         </is>
       </c>
       <c r="B918" s="5" t="n">
@@ -12404,7 +12404,7 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>fulfilled of SALUD</t>
+          <t>TUR01CUX03 Validación turno</t>
         </is>
       </c>
       <c r="B920" s="5" t="n">
@@ -12417,7 +12417,7 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>fulfilled of Happy Path</t>
+          <t>TUR01CUX03 Seleccionar hora - Por Fecha</t>
         </is>
       </c>
       <c r="B921" s="5" t="n">
@@ -12430,7 +12430,7 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>fulfilled of ADICCIONES</t>
+          <t>EDU04CUX30 Celu en el aula</t>
         </is>
       </c>
       <c r="B922" s="5" t="n">
@@ -12443,7 +12443,7 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>📅 Sacar un turno</t>
+          <t>EDU05CUX02 * Estudio en BA</t>
         </is>
       </c>
       <c r="B923" s="5" t="n">
@@ -12454,15 +12454,223 @@
       </c>
     </row>
     <row r="924">
-      <c r="A924" s="7" t="inlineStr">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>TUR01CUX13 Ya tenía turno</t>
+        </is>
+      </c>
+      <c r="B924" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C924" s="6" t="n">
+        <v>5.050946370566721e-07</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>Test IABA Feedback</t>
+        </is>
+      </c>
+      <c r="B925" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C925" s="6" t="n">
+        <v>5.050946370566721e-07</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>Test.apertura.filaCero</t>
+        </is>
+      </c>
+      <c r="B926" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C926" s="6" t="n">
+        <v>5.050946370566721e-07</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>DH11CUX08 Pedido de datos</t>
+        </is>
+      </c>
+      <c r="B927" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C927" s="6" t="n">
+        <v>5.050946370566721e-07</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>DH11CUX05 Repaso V5</t>
+        </is>
+      </c>
+      <c r="B928" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C928" s="6" t="n">
+        <v>5.050946370566721e-07</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>DH11CUX05 V4</t>
+        </is>
+      </c>
+      <c r="B929" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C929" s="6" t="n">
+        <v>5.050946370566721e-07</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>DH11CUX05 V5</t>
+        </is>
+      </c>
+      <c r="B930" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C930" s="6" t="n">
+        <v>5.050946370566721e-07</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>EDU03CUX09 Tengo una duda</t>
+        </is>
+      </c>
+      <c r="B931" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C931" s="6" t="n">
+        <v>5.050946370566721e-07</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>DH11CUX07 Validación de datos</t>
+        </is>
+      </c>
+      <c r="B932" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C932" s="6" t="n">
+        <v>5.050946370566721e-07</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>Derivacion especialista</t>
+        </is>
+      </c>
+      <c r="B933" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C933" s="6" t="n">
+        <v>5.050946370566721e-07</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>Derivación desde la web</t>
+        </is>
+      </c>
+      <c r="B934" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C934" s="6" t="n">
+        <v>5.050946370566721e-07</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>Disambiguation Intent</t>
+        </is>
+      </c>
+      <c r="B935" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C935" s="6" t="n">
+        <v>5.050946370566721e-07</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>Ubicación no encontrada | Ecobici</t>
+        </is>
+      </c>
+      <c r="B936" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C936" s="6" t="n">
+        <v>5.050946370566721e-07</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>AM02CUX03 Mapa de refugios</t>
+        </is>
+      </c>
+      <c r="B937" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C937" s="6" t="n">
+        <v>5.050946370566721e-07</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>AM03CUX04 Cuidados del agua</t>
+        </is>
+      </c>
+      <c r="B938" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C938" s="6" t="n">
+        <v>5.050946370566721e-07</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>📅 Sacar un turno</t>
+        </is>
+      </c>
+      <c r="B939" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C939" s="6" t="n">
+        <v>5.050946370566721e-07</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B924" s="8" t="n">
+      <c r="B940" s="8" t="n">
         <v>1979827</v>
       </c>
-      <c r="C924" s="9" t="n">
+      <c r="C940" s="9" t="n">
         <v>1</v>
       </c>
     </row>
